--- a/Data/Population/1992-2022.xlsx
+++ b/Data/Population/1992-2022.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://6kmwxn-my.sharepoint.com/personal/kanggle_globalinfectiousdisease_com/Documents/XMU/likangguo/2024/13 NIDS TH/Code/Data/Population/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="276" documentId="11_AD4DA82427541F7ACA7EB83DB8CE2D986AE8DE17" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34BB4001-A0A5-4E22-865E-3AD35DE8690B}"/>
+  <xr:revisionPtr revIDLastSave="279" documentId="11_AD4DA82427541F7ACA7EB83DB8CE2D986AE8DE17" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7ED4269-DAD9-4462-9160-3A5E477A3B34}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Introduction" sheetId="2" r:id="rId1"/>
     <sheet name="age" sheetId="1" r:id="rId2"/>
-    <sheet name="age_un" sheetId="3" r:id="rId3"/>
-    <sheet name="province" sheetId="4" r:id="rId4"/>
+    <sheet name="province" sheetId="4" r:id="rId3"/>
+    <sheet name="age_un" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="115">
   <si>
     <t>YEAR</t>
   </si>
@@ -165,6 +165,240 @@
   <si>
     <t>Using 2022 to represent 2023</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Bangkok</t>
+  </si>
+  <si>
+    <t>Nonthaburi</t>
+  </si>
+  <si>
+    <t>P.Nakhon S.Ayutthaya</t>
+  </si>
+  <si>
+    <t>Pathum Thani</t>
+  </si>
+  <si>
+    <t>Saraburi</t>
+  </si>
+  <si>
+    <t>Ang Thong</t>
+  </si>
+  <si>
+    <t>Chai Nat</t>
+  </si>
+  <si>
+    <t>Lop Buri</t>
+  </si>
+  <si>
+    <t>Sing Buri</t>
+  </si>
+  <si>
+    <t>Chachoengsao</t>
+  </si>
+  <si>
+    <t>Nakhon Nayok</t>
+  </si>
+  <si>
+    <t>Prachin Buri</t>
+  </si>
+  <si>
+    <t>Sa Kaeo</t>
+  </si>
+  <si>
+    <t>Samut Prakan</t>
+  </si>
+  <si>
+    <t>Kanchanaburi</t>
+  </si>
+  <si>
+    <t>Nakhon Pathom</t>
+  </si>
+  <si>
+    <t>Ratchaburi</t>
+  </si>
+  <si>
+    <t>Suphan Buri</t>
+  </si>
+  <si>
+    <t>Phetchaburi</t>
+  </si>
+  <si>
+    <t>Prachuap Khiri Khan</t>
+  </si>
+  <si>
+    <t>Samut Sakhon</t>
+  </si>
+  <si>
+    <t>Samut Songkhram</t>
+  </si>
+  <si>
+    <t>Chanthaburi</t>
+  </si>
+  <si>
+    <t>Chon Buri</t>
+  </si>
+  <si>
+    <t>Rayong</t>
+  </si>
+  <si>
+    <t>Trat</t>
+  </si>
+  <si>
+    <t>Chumphon</t>
+  </si>
+  <si>
+    <t>Nakhon Si Thammarat</t>
+  </si>
+  <si>
+    <t>Phatthalung</t>
+  </si>
+  <si>
+    <t>Surat Thani</t>
+  </si>
+  <si>
+    <t>Krabi</t>
+  </si>
+  <si>
+    <t>Phangnga</t>
+  </si>
+  <si>
+    <t>Phuket</t>
+  </si>
+  <si>
+    <t>Ranong</t>
+  </si>
+  <si>
+    <t>Trang</t>
+  </si>
+  <si>
+    <t>Narathiwat</t>
+  </si>
+  <si>
+    <t>Pattani</t>
+  </si>
+  <si>
+    <t>Satun</t>
+  </si>
+  <si>
+    <t>Songkhla</t>
+  </si>
+  <si>
+    <t>Yala</t>
+  </si>
+  <si>
+    <t>Bungkan</t>
+  </si>
+  <si>
+    <t>Loei</t>
+  </si>
+  <si>
+    <t>Nong Bua Lam Phu</t>
+  </si>
+  <si>
+    <t>Nong Khai</t>
+  </si>
+  <si>
+    <t>Udon Thani</t>
+  </si>
+  <si>
+    <t>Mukdahan</t>
+  </si>
+  <si>
+    <t>Nakhon Phanom</t>
+  </si>
+  <si>
+    <t>Sakon Nakhon</t>
+  </si>
+  <si>
+    <t>Kalasin</t>
+  </si>
+  <si>
+    <t>Khon Kaen</t>
+  </si>
+  <si>
+    <t>Maha Sarakham</t>
+  </si>
+  <si>
+    <t>Roi Et</t>
+  </si>
+  <si>
+    <t>Amnat Charoen</t>
+  </si>
+  <si>
+    <t>Si Sa Ket</t>
+  </si>
+  <si>
+    <t>Ubon Ratchathani</t>
+  </si>
+  <si>
+    <t>Yasothon</t>
+  </si>
+  <si>
+    <t>Buri Ram</t>
+  </si>
+  <si>
+    <t>Chaiyaphum</t>
+  </si>
+  <si>
+    <t>Nakhon Ratchasima</t>
+  </si>
+  <si>
+    <t>Surin</t>
+  </si>
+  <si>
+    <t>Chiang Mai</t>
+  </si>
+  <si>
+    <t>Lampang</t>
+  </si>
+  <si>
+    <t>Lamphun</t>
+  </si>
+  <si>
+    <t>Mae Hong Son</t>
+  </si>
+  <si>
+    <t>Chiang Rai</t>
+  </si>
+  <si>
+    <t>Nan</t>
+  </si>
+  <si>
+    <t>Phayao</t>
+  </si>
+  <si>
+    <t>Phrae</t>
+  </si>
+  <si>
+    <t>Phetchabun</t>
+  </si>
+  <si>
+    <t>Phitsanulok</t>
+  </si>
+  <si>
+    <t>Sukhothai</t>
+  </si>
+  <si>
+    <t>Tak</t>
+  </si>
+  <si>
+    <t>Uttaradit</t>
+  </si>
+  <si>
+    <t>Kamphaeng Phet</t>
+  </si>
+  <si>
+    <t>Nakhon Sawan</t>
+  </si>
+  <si>
+    <t>Phichit</t>
+  </si>
+  <si>
+    <t>Uthai Thani</t>
   </si>
 </sst>
 </file>
@@ -172,8 +406,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="180" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="182" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="177" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -248,8 +482,8 @@
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -260,24 +494,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="182" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="12">
     <dxf>
-      <numFmt numFmtId="180" formatCode="0.00_);[Red]\(0.00\)"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -289,7 +517,34 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <charset val="134"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <charset val="134"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <charset val="134"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -313,27 +568,6 @@
         <scheme val="minor"/>
       </font>
     </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <charset val="134"/>
-      </font>
-      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <charset val="134"/>
-      </font>
-      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <charset val="134"/>
-      </font>
-      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -348,23 +582,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3F442264-A09C-468A-844F-66F1D4245C28}" name="表2" displayName="表2" ref="A1:C3" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3F442264-A09C-468A-844F-66F1D4245C28}" name="表2" displayName="表2" ref="A1:C3" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
   <autoFilter ref="A1:C3" xr:uid="{3F442264-A09C-468A-844F-66F1D4245C28}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{997E8495-D8F4-4A47-A899-A7A32E78A655}" name="Year" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{84278821-E3B1-4B74-A14A-CB1846A0C4AC}" name="Age group" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{F5485CC2-BEE3-4F3E-BF93-BB4197E8173A}" name="Province group" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{997E8495-D8F4-4A47-A899-A7A32E78A655}" name="Year" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{84278821-E3B1-4B74-A14A-CB1846A0C4AC}" name="Age group" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{F5485CC2-BEE3-4F3E-BF93-BB4197E8173A}" name="Province group" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{7AB2D1C8-EEB6-48E3-BBC5-03E05CCB82C5}" name="表3" displayName="表3" ref="A2:X7" totalsRowShown="0" headerRowDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{7AB2D1C8-EEB6-48E3-BBC5-03E05CCB82C5}" name="表3" displayName="表3" ref="A2:X7" totalsRowShown="0" headerRowDxfId="6">
   <autoFilter ref="A2:X7" xr:uid="{7AB2D1C8-EEB6-48E3-BBC5-03E05CCB82C5}"/>
   <tableColumns count="24">
     <tableColumn id="1" xr3:uid="{5F5FA6ED-F131-4ABB-8B98-F1DBBA099E33}" name="Year"/>
-    <tableColumn id="2" xr3:uid="{BF85B206-A0D6-4122-B91B-A9531011EE9E}" name="0-4" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{BF85B206-A0D6-4122-B91B-A9531011EE9E}" name="0-4" dataDxfId="5"/>
     <tableColumn id="3" xr3:uid="{8FAE4D95-B414-4F48-88C3-46A79D55B1C0}" name="5-9"/>
     <tableColumn id="4" xr3:uid="{09B69DF3-D366-4DBC-A2FF-B5B7D435B84B}" name="10-14"/>
     <tableColumn id="5" xr3:uid="{4128ED10-5597-407E-AA32-9F0082215A9E}" name="15-19"/>
@@ -377,7 +611,7 @@
     <tableColumn id="12" xr3:uid="{00CF7582-B6BF-4CA8-99C1-A8E6D4E772C7}" name="50-54"/>
     <tableColumn id="13" xr3:uid="{D443DF0E-35EA-4E04-BCF4-FDC7D1A3EAEB}" name="55-59"/>
     <tableColumn id="14" xr3:uid="{A4EED2F2-806B-4239-BD78-73A150F91E22}" name="60-64"/>
-    <tableColumn id="15" xr3:uid="{83CDBD91-9764-4F60-A95B-B9141F52A6CC}" name="65+" dataDxfId="0">
+    <tableColumn id="15" xr3:uid="{83CDBD91-9764-4F60-A95B-B9141F52A6CC}" name="65+" dataDxfId="4">
       <calculatedColumnFormula>SUM(P3:W3)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="16" xr3:uid="{9A996CEE-4530-465E-BFF0-7953D7C58B99}" name="65-69"/>
@@ -399,7 +633,7 @@
   <autoFilter ref="A9:X14" xr:uid="{E425CAF8-A05B-493D-9576-D5B11152E32A}"/>
   <tableColumns count="24">
     <tableColumn id="1" xr3:uid="{890E246C-5A6C-4CCA-89EC-A0A263B3B6CA}" name="Year"/>
-    <tableColumn id="2" xr3:uid="{EA2AE1F2-BA16-421B-9FFB-5C853773616E}" name="0-4" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{EA2AE1F2-BA16-421B-9FFB-5C853773616E}" name="0-4" dataDxfId="2"/>
     <tableColumn id="3" xr3:uid="{4EFB77E4-FC6D-4B19-B6C6-68C0E2082D42}" name="5-9"/>
     <tableColumn id="4" xr3:uid="{0B937AE8-5F3E-40C7-869E-605B0E34531B}" name="10-14"/>
     <tableColumn id="5" xr3:uid="{B3459115-64E4-49D3-931D-D557BE051E36}" name="15-19"/>
@@ -428,11 +662,11 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{B8D06390-96E2-4752-AD39-2A22000D50E8}" name="表4_6" displayName="表4_6" ref="A16:O21" totalsRowShown="0" headerRowDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{B8D06390-96E2-4752-AD39-2A22000D50E8}" name="表4_6" displayName="表4_6" ref="A16:O21" totalsRowShown="0" headerRowDxfId="1">
   <autoFilter ref="A16:O21" xr:uid="{B8D06390-96E2-4752-AD39-2A22000D50E8}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{42580EA9-DB8F-4146-BE5E-2DCD1900C58F}" name="Year"/>
-    <tableColumn id="2" xr3:uid="{4C3342B0-1C0A-4408-981F-D7E1B82083E8}" name="0-4" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{4C3342B0-1C0A-4408-981F-D7E1B82083E8}" name="0-4" dataDxfId="0"/>
     <tableColumn id="3" xr3:uid="{6FC0A4C7-DBB4-47DB-B7FB-17052A94CDDE}" name="5-9"/>
     <tableColumn id="4" xr3:uid="{4F249022-FBD2-4F65-80CF-60DE53F3FC1D}" name="10-14"/>
     <tableColumn id="5" xr3:uid="{912066C7-F640-4EAF-A9C1-E1073B7A26F3}" name="15-19"/>
@@ -715,14 +949,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{669A8012-AA46-4279-8E56-003C061CE7F3}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="56.875" customWidth="1"/>
+    <col min="2" max="2" width="56.88671875" customWidth="1"/>
     <col min="3" max="3" width="57" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A1" s="5" t="s">
         <v>18</v>
       </c>
@@ -733,7 +967,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="46.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>19</v>
       </c>
@@ -744,7 +978,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>2023</v>
       </c>
@@ -767,13 +1001,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P33"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="15" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.375" customWidth="1"/>
+    <col min="2" max="15" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -823,7 +1057,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1992</v>
       </c>
@@ -873,7 +1107,7 @@
         <v>57374998</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1993</v>
       </c>
@@ -923,7 +1157,7 @@
         <v>58062523</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1994</v>
       </c>
@@ -973,7 +1207,7 @@
         <v>58715746</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1995</v>
       </c>
@@ -1023,7 +1257,7 @@
         <v>59277900</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1996</v>
       </c>
@@ -1073,7 +1307,7 @@
         <v>59788284</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1997</v>
       </c>
@@ -1123,7 +1357,7 @@
         <v>60466243</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1998</v>
       </c>
@@ -1173,7 +1407,7 @@
         <v>61155888</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1999</v>
       </c>
@@ -1223,7 +1457,7 @@
         <v>61563980</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2000</v>
       </c>
@@ -1273,7 +1507,7 @@
         <v>61770259</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2001</v>
       </c>
@@ -1323,7 +1557,7 @@
         <v>62093855</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2002</v>
       </c>
@@ -1373,7 +1607,7 @@
         <v>62554413</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2003</v>
       </c>
@@ -1423,7 +1657,7 @@
         <v>62939819</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2004</v>
       </c>
@@ -1473,7 +1707,7 @@
         <v>62526710</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2005</v>
       </c>
@@ -1523,7 +1757,7 @@
         <v>62195878</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2006</v>
       </c>
@@ -1573,7 +1807,7 @@
         <v>62623416</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2007</v>
       </c>
@@ -1623,7 +1857,7 @@
         <v>62933515</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2008</v>
       </c>
@@ -1673,7 +1907,7 @@
         <v>63214022</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2009</v>
       </c>
@@ -1723,7 +1957,7 @@
         <v>63457439</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2010</v>
       </c>
@@ -1773,7 +2007,7 @@
         <v>63701703</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2011</v>
       </c>
@@ -1823,7 +2057,7 @@
         <v>64181001</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2012</v>
       </c>
@@ -1873,7 +2107,7 @@
         <v>64266404</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2013</v>
       </c>
@@ -1923,7 +2157,7 @@
         <v>64621302</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2014</v>
       </c>
@@ -1973,7 +2207,7 @@
         <v>64955313</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2015</v>
       </c>
@@ -2023,7 +2257,7 @@
         <v>65426907</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2016</v>
       </c>
@@ -2073,7 +2307,7 @@
         <v>65830324</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2017</v>
       </c>
@@ -2123,7 +2357,7 @@
         <v>66060027</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2018</v>
       </c>
@@ -2173,7 +2407,7 @@
         <v>64726085</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2019</v>
       </c>
@@ -2223,7 +2457,7 @@
         <v>64872999</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>2020</v>
       </c>
@@ -2273,7 +2507,7 @@
         <v>66372831</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2021</v>
       </c>
@@ -2323,7 +2557,7 @@
         <v>66179083</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>2022</v>
       </c>
@@ -2373,53 +2607,53 @@
         <v>66130957</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A33" s="9">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A33" s="8">
         <v>2023</v>
       </c>
-      <c r="B33" s="10">
+      <c r="B33" s="9">
         <v>2849971</v>
       </c>
-      <c r="C33" s="10">
+      <c r="C33" s="9">
         <v>3558725</v>
       </c>
-      <c r="D33" s="10">
+      <c r="D33" s="9">
         <v>3895566</v>
       </c>
-      <c r="E33" s="10">
+      <c r="E33" s="9">
         <v>3986357</v>
       </c>
-      <c r="F33" s="10">
+      <c r="F33" s="9">
         <v>4219252</v>
       </c>
-      <c r="G33" s="10">
+      <c r="G33" s="9">
         <v>4794222</v>
       </c>
-      <c r="H33" s="10">
+      <c r="H33" s="9">
         <v>4593288</v>
       </c>
-      <c r="I33" s="10">
+      <c r="I33" s="9">
         <v>4706901</v>
       </c>
-      <c r="J33" s="10">
+      <c r="J33" s="9">
         <v>5064422</v>
       </c>
-      <c r="K33" s="10">
+      <c r="K33" s="9">
         <v>5093377</v>
       </c>
-      <c r="L33" s="10">
+      <c r="L33" s="9">
         <v>5117831</v>
       </c>
-      <c r="M33" s="10">
+      <c r="M33" s="9">
         <v>4736375</v>
       </c>
-      <c r="N33" s="10">
+      <c r="N33" s="9">
         <v>3952987</v>
       </c>
-      <c r="O33" s="10">
+      <c r="O33" s="9">
         <v>8342917</v>
       </c>
-      <c r="P33" s="10">
+      <c r="P33" s="9">
         <v>66130957</v>
       </c>
     </row>
@@ -2430,50 +2664,4351 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41BEA482-6B4D-415D-9895-A94933E586DE}">
+  <dimension ref="A1:CA18"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K1" t="s">
+        <v>46</v>
+      </c>
+      <c r="L1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N1" t="s">
+        <v>49</v>
+      </c>
+      <c r="O1" t="s">
+        <v>50</v>
+      </c>
+      <c r="P1" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>52</v>
+      </c>
+      <c r="R1" t="s">
+        <v>53</v>
+      </c>
+      <c r="S1" t="s">
+        <v>54</v>
+      </c>
+      <c r="T1" t="s">
+        <v>55</v>
+      </c>
+      <c r="U1" t="s">
+        <v>56</v>
+      </c>
+      <c r="V1" t="s">
+        <v>57</v>
+      </c>
+      <c r="W1" t="s">
+        <v>58</v>
+      </c>
+      <c r="X1" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>75</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>77</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>78</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>79</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>80</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>85</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>87</v>
+      </c>
+      <c r="BA1" t="s">
+        <v>88</v>
+      </c>
+      <c r="BB1" t="s">
+        <v>89</v>
+      </c>
+      <c r="BC1" t="s">
+        <v>90</v>
+      </c>
+      <c r="BD1" t="s">
+        <v>91</v>
+      </c>
+      <c r="BE1" t="s">
+        <v>92</v>
+      </c>
+      <c r="BF1" t="s">
+        <v>93</v>
+      </c>
+      <c r="BG1" t="s">
+        <v>94</v>
+      </c>
+      <c r="BH1" t="s">
+        <v>95</v>
+      </c>
+      <c r="BI1" t="s">
+        <v>96</v>
+      </c>
+      <c r="BJ1" t="s">
+        <v>97</v>
+      </c>
+      <c r="BK1" t="s">
+        <v>98</v>
+      </c>
+      <c r="BL1" t="s">
+        <v>99</v>
+      </c>
+      <c r="BM1" t="s">
+        <v>100</v>
+      </c>
+      <c r="BN1" t="s">
+        <v>101</v>
+      </c>
+      <c r="BO1" t="s">
+        <v>102</v>
+      </c>
+      <c r="BP1" t="s">
+        <v>103</v>
+      </c>
+      <c r="BQ1" t="s">
+        <v>104</v>
+      </c>
+      <c r="BR1" t="s">
+        <v>105</v>
+      </c>
+      <c r="BS1" t="s">
+        <v>106</v>
+      </c>
+      <c r="BT1" t="s">
+        <v>107</v>
+      </c>
+      <c r="BU1" t="s">
+        <v>108</v>
+      </c>
+      <c r="BV1" t="s">
+        <v>109</v>
+      </c>
+      <c r="BW1" t="s">
+        <v>110</v>
+      </c>
+      <c r="BX1" t="s">
+        <v>111</v>
+      </c>
+      <c r="BY1" t="s">
+        <v>112</v>
+      </c>
+      <c r="BZ1" t="s">
+        <v>113</v>
+      </c>
+      <c r="CA1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="2" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>2007</v>
+      </c>
+      <c r="B2">
+        <v>62933515</v>
+      </c>
+      <c r="C2">
+        <v>5706103</v>
+      </c>
+      <c r="D2">
+        <v>1011624</v>
+      </c>
+      <c r="E2">
+        <v>757654</v>
+      </c>
+      <c r="F2">
+        <v>879091</v>
+      </c>
+      <c r="G2">
+        <v>612806</v>
+      </c>
+      <c r="H2">
+        <v>284175</v>
+      </c>
+      <c r="I2">
+        <v>338077</v>
+      </c>
+      <c r="J2">
+        <v>751298</v>
+      </c>
+      <c r="K2">
+        <v>216311</v>
+      </c>
+      <c r="L2">
+        <v>656586</v>
+      </c>
+      <c r="M2">
+        <v>249250</v>
+      </c>
+      <c r="N2">
+        <v>454404</v>
+      </c>
+      <c r="O2">
+        <v>538741</v>
+      </c>
+      <c r="P2">
+        <v>1117284</v>
+      </c>
+      <c r="Q2">
+        <v>834865</v>
+      </c>
+      <c r="R2">
+        <v>826438</v>
+      </c>
+      <c r="S2">
+        <v>830184</v>
+      </c>
+      <c r="T2">
+        <v>843245</v>
+      </c>
+      <c r="U2">
+        <v>456371</v>
+      </c>
+      <c r="V2">
+        <v>494502</v>
+      </c>
+      <c r="W2">
+        <v>466222</v>
+      </c>
+      <c r="X2">
+        <v>194602</v>
+      </c>
+      <c r="Y2">
+        <v>503197</v>
+      </c>
+      <c r="Z2">
+        <v>1221369</v>
+      </c>
+      <c r="AA2">
+        <v>578628</v>
+      </c>
+      <c r="AB2">
+        <v>220246</v>
+      </c>
+      <c r="AC2">
+        <v>480131</v>
+      </c>
+      <c r="AD2">
+        <v>1508729</v>
+      </c>
+      <c r="AE2">
+        <v>502943</v>
+      </c>
+      <c r="AF2">
+        <v>965561</v>
+      </c>
+      <c r="AG2">
+        <v>406999</v>
+      </c>
+      <c r="AH2">
+        <v>246141</v>
+      </c>
+      <c r="AI2">
+        <v>308118</v>
+      </c>
+      <c r="AJ2">
+        <v>180319</v>
+      </c>
+      <c r="AK2">
+        <v>608892</v>
+      </c>
+      <c r="AL2">
+        <v>709345</v>
+      </c>
+      <c r="AM2">
+        <v>636768</v>
+      </c>
+      <c r="AN2">
+        <v>283014</v>
+      </c>
+      <c r="AO2">
+        <v>1321209</v>
+      </c>
+      <c r="AP2">
+        <v>469472</v>
+      </c>
+      <c r="AR2">
+        <v>614421</v>
+      </c>
+      <c r="AS2">
+        <v>497148</v>
+      </c>
+      <c r="AT2">
+        <v>901100</v>
+      </c>
+      <c r="AU2">
+        <v>1529124</v>
+      </c>
+      <c r="AV2">
+        <v>335778</v>
+      </c>
+      <c r="AW2">
+        <v>696229</v>
+      </c>
+      <c r="AX2">
+        <v>1111056</v>
+      </c>
+      <c r="AY2">
+        <v>976536</v>
+      </c>
+      <c r="AZ2">
+        <v>1751458</v>
+      </c>
+      <c r="BA2">
+        <v>936846</v>
+      </c>
+      <c r="BB2">
+        <v>1309318</v>
+      </c>
+      <c r="BC2">
+        <v>368925</v>
+      </c>
+      <c r="BD2">
+        <v>1444748</v>
+      </c>
+      <c r="BE2">
+        <v>1784372</v>
+      </c>
+      <c r="BF2">
+        <v>540216</v>
+      </c>
+      <c r="BG2">
+        <v>1536396</v>
+      </c>
+      <c r="BH2">
+        <v>1119372</v>
+      </c>
+      <c r="BI2">
+        <v>2554241</v>
+      </c>
+      <c r="BJ2">
+        <v>1373965</v>
+      </c>
+      <c r="BK2">
+        <v>1661349</v>
+      </c>
+      <c r="BL2">
+        <v>772202</v>
+      </c>
+      <c r="BM2">
+        <v>405361</v>
+      </c>
+      <c r="BN2">
+        <v>254990</v>
+      </c>
+      <c r="BO2">
+        <v>1225364</v>
+      </c>
+      <c r="BP2">
+        <v>477522</v>
+      </c>
+      <c r="BQ2">
+        <v>486399</v>
+      </c>
+      <c r="BR2">
+        <v>467125</v>
+      </c>
+      <c r="BS2">
+        <v>999924</v>
+      </c>
+      <c r="BT2">
+        <v>843096</v>
+      </c>
+      <c r="BU2">
+        <v>607061</v>
+      </c>
+      <c r="BV2">
+        <v>529303</v>
+      </c>
+      <c r="BW2">
+        <v>466380</v>
+      </c>
+      <c r="BX2">
+        <v>727158</v>
+      </c>
+      <c r="BY2">
+        <v>1074849</v>
+      </c>
+      <c r="BZ2">
+        <v>556287</v>
+      </c>
+      <c r="CA2">
+        <v>326982</v>
+      </c>
+    </row>
+    <row r="3" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2008</v>
+      </c>
+      <c r="B3">
+        <v>63214022</v>
+      </c>
+      <c r="C3">
+        <v>5713566</v>
+      </c>
+      <c r="D3">
+        <v>1038392</v>
+      </c>
+      <c r="E3">
+        <v>764919</v>
+      </c>
+      <c r="F3">
+        <v>913047</v>
+      </c>
+      <c r="G3">
+        <v>618699</v>
+      </c>
+      <c r="H3">
+        <v>284619</v>
+      </c>
+      <c r="I3">
+        <v>336550</v>
+      </c>
+      <c r="J3">
+        <v>751811</v>
+      </c>
+      <c r="K3">
+        <v>215602</v>
+      </c>
+      <c r="L3">
+        <v>661898</v>
+      </c>
+      <c r="M3">
+        <v>249625</v>
+      </c>
+      <c r="N3">
+        <v>457184</v>
+      </c>
+      <c r="O3">
+        <v>540281</v>
+      </c>
+      <c r="P3">
+        <v>1137082</v>
+      </c>
+      <c r="Q3">
+        <v>838094</v>
+      </c>
+      <c r="R3">
+        <v>837285</v>
+      </c>
+      <c r="S3">
+        <v>833650</v>
+      </c>
+      <c r="T3">
+        <v>843541</v>
+      </c>
+      <c r="U3">
+        <v>457518</v>
+      </c>
+      <c r="V3">
+        <v>497483</v>
+      </c>
+      <c r="W3">
+        <v>474041</v>
+      </c>
+      <c r="X3">
+        <v>194134</v>
+      </c>
+      <c r="Y3">
+        <v>506012</v>
+      </c>
+      <c r="Z3">
+        <v>1249067</v>
+      </c>
+      <c r="AA3">
+        <v>591067</v>
+      </c>
+      <c r="AB3">
+        <v>221185</v>
+      </c>
+      <c r="AC3">
+        <v>483011</v>
+      </c>
+      <c r="AD3">
+        <v>1510081</v>
+      </c>
+      <c r="AE3">
+        <v>503847</v>
+      </c>
+      <c r="AF3">
+        <v>976956</v>
+      </c>
+      <c r="AG3">
+        <v>414670</v>
+      </c>
+      <c r="AH3">
+        <v>248411</v>
+      </c>
+      <c r="AI3">
+        <v>321252</v>
+      </c>
+      <c r="AJ3">
+        <v>181758</v>
+      </c>
+      <c r="AK3">
+        <v>612601</v>
+      </c>
+      <c r="AL3">
+        <v>715724</v>
+      </c>
+      <c r="AM3">
+        <v>639988</v>
+      </c>
+      <c r="AN3">
+        <v>286446</v>
+      </c>
+      <c r="AO3">
+        <v>1330342</v>
+      </c>
+      <c r="AP3">
+        <v>473109</v>
+      </c>
+      <c r="AR3">
+        <v>616981</v>
+      </c>
+      <c r="AS3">
+        <v>498562</v>
+      </c>
+      <c r="AT3">
+        <v>904748</v>
+      </c>
+      <c r="AU3">
+        <v>1533158</v>
+      </c>
+      <c r="AV3">
+        <v>336802</v>
+      </c>
+      <c r="AW3">
+        <v>698235</v>
+      </c>
+      <c r="AX3">
+        <v>1114550</v>
+      </c>
+      <c r="AY3">
+        <v>978046</v>
+      </c>
+      <c r="AZ3">
+        <v>1754258</v>
+      </c>
+      <c r="BA3">
+        <v>936430</v>
+      </c>
+      <c r="BB3">
+        <v>1307901</v>
+      </c>
+      <c r="BC3">
+        <v>369196</v>
+      </c>
+      <c r="BD3">
+        <v>1442212</v>
+      </c>
+      <c r="BE3">
+        <v>1790581</v>
+      </c>
+      <c r="BF3">
+        <v>539414</v>
+      </c>
+      <c r="BG3">
+        <v>1538861</v>
+      </c>
+      <c r="BH3">
+        <v>1121123</v>
+      </c>
+      <c r="BI3">
+        <v>2559006</v>
+      </c>
+      <c r="BJ3">
+        <v>1374116</v>
+      </c>
+      <c r="BK3">
+        <v>1667358</v>
+      </c>
+      <c r="BL3">
+        <v>769115</v>
+      </c>
+      <c r="BM3">
+        <v>405141</v>
+      </c>
+      <c r="BN3">
+        <v>253748</v>
+      </c>
+      <c r="BO3">
+        <v>1226165</v>
+      </c>
+      <c r="BP3">
+        <v>476683</v>
+      </c>
+      <c r="BQ3">
+        <v>486983</v>
+      </c>
+      <c r="BR3">
+        <v>464677</v>
+      </c>
+      <c r="BS3">
+        <v>996882</v>
+      </c>
+      <c r="BT3">
+        <v>842840</v>
+      </c>
+      <c r="BU3">
+        <v>604559</v>
+      </c>
+      <c r="BV3">
+        <v>534629</v>
+      </c>
+      <c r="BW3">
+        <v>464741</v>
+      </c>
+      <c r="BX3">
+        <v>726104</v>
+      </c>
+      <c r="BY3">
+        <v>1073962</v>
+      </c>
+      <c r="BZ3">
+        <v>554426</v>
+      </c>
+      <c r="CA3">
+        <v>327281</v>
+      </c>
+    </row>
+    <row r="4" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2009</v>
+      </c>
+      <c r="B4">
+        <v>63457439</v>
+      </c>
+      <c r="C4">
+        <v>5706739</v>
+      </c>
+      <c r="D4">
+        <v>1065332</v>
+      </c>
+      <c r="E4">
+        <v>772142</v>
+      </c>
+      <c r="F4">
+        <v>942813</v>
+      </c>
+      <c r="G4">
+        <v>617174</v>
+      </c>
+      <c r="H4">
+        <v>284819</v>
+      </c>
+      <c r="I4">
+        <v>335686</v>
+      </c>
+      <c r="J4">
+        <v>754127</v>
+      </c>
+      <c r="K4">
+        <v>215426</v>
+      </c>
+      <c r="L4">
+        <v>666907</v>
+      </c>
+      <c r="M4">
+        <v>251219</v>
+      </c>
+      <c r="N4">
+        <v>460617</v>
+      </c>
+      <c r="O4">
+        <v>541939</v>
+      </c>
+      <c r="P4">
+        <v>1155665</v>
+      </c>
+      <c r="Q4">
+        <v>837165</v>
+      </c>
+      <c r="R4">
+        <v>847513</v>
+      </c>
+      <c r="S4">
+        <v>835546</v>
+      </c>
+      <c r="T4">
+        <v>844545</v>
+      </c>
+      <c r="U4">
+        <v>460108</v>
+      </c>
+      <c r="V4">
+        <v>502221</v>
+      </c>
+      <c r="W4">
+        <v>481377</v>
+      </c>
+      <c r="X4">
+        <v>193851</v>
+      </c>
+      <c r="Y4">
+        <v>509633</v>
+      </c>
+      <c r="Z4">
+        <v>1277139</v>
+      </c>
+      <c r="AA4">
+        <v>605380</v>
+      </c>
+      <c r="AB4">
+        <v>220918</v>
+      </c>
+      <c r="AC4">
+        <v>486233</v>
+      </c>
+      <c r="AD4">
+        <v>1514832</v>
+      </c>
+      <c r="AE4">
+        <v>506454</v>
+      </c>
+      <c r="AF4">
+        <v>988854</v>
+      </c>
+      <c r="AG4">
+        <v>422631</v>
+      </c>
+      <c r="AH4">
+        <v>250796</v>
+      </c>
+      <c r="AI4">
+        <v>331460</v>
+      </c>
+      <c r="AJ4">
+        <v>182242</v>
+      </c>
+      <c r="AK4">
+        <v>616773</v>
+      </c>
+      <c r="AL4">
+        <v>724001</v>
+      </c>
+      <c r="AM4">
+        <v>644897</v>
+      </c>
+      <c r="AN4">
+        <v>290755</v>
+      </c>
+      <c r="AO4">
+        <v>1339861</v>
+      </c>
+      <c r="AP4">
+        <v>477931</v>
+      </c>
+      <c r="AR4">
+        <v>619602</v>
+      </c>
+      <c r="AS4">
+        <v>500217</v>
+      </c>
+      <c r="AT4">
+        <v>907064</v>
+      </c>
+      <c r="AU4">
+        <v>1537285</v>
+      </c>
+      <c r="AV4">
+        <v>337773</v>
+      </c>
+      <c r="AW4">
+        <v>700027</v>
+      </c>
+      <c r="AX4">
+        <v>1117242</v>
+      </c>
+      <c r="AY4">
+        <v>979371</v>
+      </c>
+      <c r="AZ4">
+        <v>1759172</v>
+      </c>
+      <c r="BA4">
+        <v>937972</v>
+      </c>
+      <c r="BB4">
+        <v>1307686</v>
+      </c>
+      <c r="BC4">
+        <v>370141</v>
+      </c>
+      <c r="BD4">
+        <v>1443879</v>
+      </c>
+      <c r="BE4">
+        <v>1799604</v>
+      </c>
+      <c r="BF4">
+        <v>539210</v>
+      </c>
+      <c r="BG4">
+        <v>1544218</v>
+      </c>
+      <c r="BH4">
+        <v>1123907</v>
+      </c>
+      <c r="BI4">
+        <v>2568205</v>
+      </c>
+      <c r="BJ4">
+        <v>1376694</v>
+      </c>
+      <c r="BK4">
+        <v>1651433</v>
+      </c>
+      <c r="BL4">
+        <v>766057</v>
+      </c>
+      <c r="BM4">
+        <v>404910</v>
+      </c>
+      <c r="BN4">
+        <v>247270</v>
+      </c>
+      <c r="BO4">
+        <v>1211126</v>
+      </c>
+      <c r="BP4">
+        <v>475799</v>
+      </c>
+      <c r="BQ4">
+        <v>487254</v>
+      </c>
+      <c r="BR4">
+        <v>462784</v>
+      </c>
+      <c r="BS4">
+        <v>995679</v>
+      </c>
+      <c r="BT4">
+        <v>844779</v>
+      </c>
+      <c r="BU4">
+        <v>603316</v>
+      </c>
+      <c r="BV4">
+        <v>528997</v>
+      </c>
+      <c r="BW4">
+        <v>463579</v>
+      </c>
+      <c r="BX4">
+        <v>726530</v>
+      </c>
+      <c r="BY4">
+        <v>1073554</v>
+      </c>
+      <c r="BZ4">
+        <v>553653</v>
+      </c>
+      <c r="CA4">
+        <v>327729</v>
+      </c>
+    </row>
+    <row r="5" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>2010</v>
+      </c>
+      <c r="B5">
+        <v>63701703</v>
+      </c>
+      <c r="C5">
+        <v>5701995</v>
+      </c>
+      <c r="D5">
+        <v>1089908</v>
+      </c>
+      <c r="E5">
+        <v>778627</v>
+      </c>
+      <c r="F5">
+        <v>971010</v>
+      </c>
+      <c r="G5">
+        <v>615046</v>
+      </c>
+      <c r="H5">
+        <v>284889</v>
+      </c>
+      <c r="I5">
+        <v>335177</v>
+      </c>
+      <c r="J5">
+        <v>755153</v>
+      </c>
+      <c r="K5">
+        <v>214981</v>
+      </c>
+      <c r="L5">
+        <v>671458</v>
+      </c>
+      <c r="M5">
+        <v>252209</v>
+      </c>
+      <c r="N5">
+        <v>464213</v>
+      </c>
+      <c r="O5">
+        <v>543276</v>
+      </c>
+      <c r="P5">
+        <v>1174643</v>
+      </c>
+      <c r="Q5">
+        <v>836600</v>
+      </c>
+      <c r="R5">
+        <v>855837</v>
+      </c>
+      <c r="S5">
+        <v>837153</v>
+      </c>
+      <c r="T5">
+        <v>845220</v>
+      </c>
+      <c r="U5">
+        <v>462636</v>
+      </c>
+      <c r="V5">
+        <v>506599</v>
+      </c>
+      <c r="W5">
+        <v>488247</v>
+      </c>
+      <c r="X5">
+        <v>193853</v>
+      </c>
+      <c r="Y5">
+        <v>512932</v>
+      </c>
+      <c r="Z5">
+        <v>1302942</v>
+      </c>
+      <c r="AA5">
+        <v>619249</v>
+      </c>
+      <c r="AB5">
+        <v>220465</v>
+      </c>
+      <c r="AC5">
+        <v>488855</v>
+      </c>
+      <c r="AD5">
+        <v>1519531</v>
+      </c>
+      <c r="AE5">
+        <v>508656</v>
+      </c>
+      <c r="AF5">
+        <v>997302</v>
+      </c>
+      <c r="AG5">
+        <v>429631</v>
+      </c>
+      <c r="AH5">
+        <v>252385</v>
+      </c>
+      <c r="AI5">
+        <v>340490</v>
+      </c>
+      <c r="AJ5">
+        <v>182417</v>
+      </c>
+      <c r="AK5">
+        <v>620668</v>
+      </c>
+      <c r="AL5">
+        <v>732617</v>
+      </c>
+      <c r="AM5">
+        <v>651442</v>
+      </c>
+      <c r="AN5">
+        <v>295133</v>
+      </c>
+      <c r="AO5">
+        <v>1350489</v>
+      </c>
+      <c r="AP5">
+        <v>483857</v>
+      </c>
+      <c r="AR5">
+        <v>622424</v>
+      </c>
+      <c r="AS5">
+        <v>501891</v>
+      </c>
+      <c r="AT5">
+        <v>910094</v>
+      </c>
+      <c r="AU5">
+        <v>1541863</v>
+      </c>
+      <c r="AV5">
+        <v>338812</v>
+      </c>
+      <c r="AW5">
+        <v>702041</v>
+      </c>
+      <c r="AX5">
+        <v>1120678</v>
+      </c>
+      <c r="AY5">
+        <v>981369</v>
+      </c>
+      <c r="AZ5">
+        <v>1764922</v>
+      </c>
+      <c r="BA5">
+        <v>940001</v>
+      </c>
+      <c r="BB5">
+        <v>1308934</v>
+      </c>
+      <c r="BC5">
+        <v>371471</v>
+      </c>
+      <c r="BD5">
+        <v>1449409</v>
+      </c>
+      <c r="BE5">
+        <v>1808422</v>
+      </c>
+      <c r="BF5">
+        <v>539196</v>
+      </c>
+      <c r="BG5">
+        <v>1550275</v>
+      </c>
+      <c r="BH5">
+        <v>1126295</v>
+      </c>
+      <c r="BI5">
+        <v>2576691</v>
+      </c>
+      <c r="BJ5">
+        <v>1379794</v>
+      </c>
+      <c r="BK5">
+        <v>1636514</v>
+      </c>
+      <c r="BL5">
+        <v>763224</v>
+      </c>
+      <c r="BM5">
+        <v>404627</v>
+      </c>
+      <c r="BN5">
+        <v>242295</v>
+      </c>
+      <c r="BO5">
+        <v>1196576</v>
+      </c>
+      <c r="BP5">
+        <v>475989</v>
+      </c>
+      <c r="BQ5">
+        <v>486713</v>
+      </c>
+      <c r="BR5">
+        <v>461423</v>
+      </c>
+      <c r="BS5">
+        <v>995578</v>
+      </c>
+      <c r="BT5">
+        <v>847627</v>
+      </c>
+      <c r="BU5">
+        <v>602296</v>
+      </c>
+      <c r="BV5">
+        <v>522673</v>
+      </c>
+      <c r="BW5">
+        <v>462785</v>
+      </c>
+      <c r="BX5">
+        <v>726970</v>
+      </c>
+      <c r="BY5">
+        <v>1073182</v>
+      </c>
+      <c r="BZ5">
+        <v>552942</v>
+      </c>
+      <c r="CA5">
+        <v>327916</v>
+      </c>
+    </row>
+    <row r="6" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>2011</v>
+      </c>
+      <c r="B6">
+        <v>63977185</v>
+      </c>
+      <c r="C6">
+        <v>5688119</v>
+      </c>
+      <c r="D6">
+        <v>1112185</v>
+      </c>
+      <c r="E6">
+        <v>784875</v>
+      </c>
+      <c r="F6">
+        <v>998271</v>
+      </c>
+      <c r="G6">
+        <v>618919</v>
+      </c>
+      <c r="H6">
+        <v>284516</v>
+      </c>
+      <c r="I6">
+        <v>334096</v>
+      </c>
+      <c r="J6">
+        <v>755991</v>
+      </c>
+      <c r="K6">
+        <v>214124</v>
+      </c>
+      <c r="L6">
+        <v>676652</v>
+      </c>
+      <c r="M6">
+        <v>253283</v>
+      </c>
+      <c r="N6">
+        <v>468113</v>
+      </c>
+      <c r="O6">
+        <v>544848</v>
+      </c>
+      <c r="P6">
+        <v>1194202</v>
+      </c>
+      <c r="Q6">
+        <v>839345</v>
+      </c>
+      <c r="R6">
+        <v>863155</v>
+      </c>
+      <c r="S6">
+        <v>840880</v>
+      </c>
+      <c r="T6">
+        <v>845452</v>
+      </c>
+      <c r="U6">
+        <v>465056</v>
+      </c>
+      <c r="V6">
+        <v>510852</v>
+      </c>
+      <c r="W6">
+        <v>495493</v>
+      </c>
+      <c r="X6">
+        <v>194072</v>
+      </c>
+      <c r="Y6">
+        <v>515736</v>
+      </c>
+      <c r="Z6">
+        <v>1327475</v>
+      </c>
+      <c r="AA6">
+        <v>632069</v>
+      </c>
+      <c r="AB6">
+        <v>221467</v>
+      </c>
+      <c r="AC6">
+        <v>491073</v>
+      </c>
+      <c r="AD6">
+        <v>1524317</v>
+      </c>
+      <c r="AE6">
+        <v>510299</v>
+      </c>
+      <c r="AF6">
+        <v>1006224</v>
+      </c>
+      <c r="AG6">
+        <v>435372</v>
+      </c>
+      <c r="AH6">
+        <v>254022</v>
+      </c>
+      <c r="AI6">
+        <v>349457</v>
+      </c>
+      <c r="AJ6">
+        <v>183464</v>
+      </c>
+      <c r="AK6">
+        <v>624684</v>
+      </c>
+      <c r="AL6">
+        <v>742268</v>
+      </c>
+      <c r="AM6">
+        <v>659373</v>
+      </c>
+      <c r="AN6">
+        <v>299315</v>
+      </c>
+      <c r="AO6">
+        <v>1362017</v>
+      </c>
+      <c r="AP6">
+        <v>490574</v>
+      </c>
+      <c r="AQ6">
+        <v>203818</v>
+      </c>
+      <c r="AR6">
+        <v>624493</v>
+      </c>
+      <c r="AS6">
+        <v>502710</v>
+      </c>
+      <c r="AT6">
+        <v>711404</v>
+      </c>
+      <c r="AU6">
+        <v>1546447</v>
+      </c>
+      <c r="AV6">
+        <v>340079</v>
+      </c>
+      <c r="AW6">
+        <v>704080</v>
+      </c>
+      <c r="AX6">
+        <v>1123129</v>
+      </c>
+      <c r="AY6">
+        <v>982117</v>
+      </c>
+      <c r="AZ6">
+        <v>1766834</v>
+      </c>
+      <c r="BA6">
+        <v>940324</v>
+      </c>
+      <c r="BB6">
+        <v>1307384</v>
+      </c>
+      <c r="BC6">
+        <v>372190</v>
+      </c>
+      <c r="BD6">
+        <v>1452338</v>
+      </c>
+      <c r="BE6">
+        <v>1814573</v>
+      </c>
+      <c r="BF6">
+        <v>539055</v>
+      </c>
+      <c r="BG6">
+        <v>1556426</v>
+      </c>
+      <c r="BH6">
+        <v>1127423</v>
+      </c>
+      <c r="BI6">
+        <v>2583707</v>
+      </c>
+      <c r="BJ6">
+        <v>1381081</v>
+      </c>
+      <c r="BK6">
+        <v>1643312</v>
+      </c>
+      <c r="BL6">
+        <v>759742</v>
+      </c>
+      <c r="BM6">
+        <v>404257</v>
+      </c>
+      <c r="BN6">
+        <v>243395</v>
+      </c>
+      <c r="BO6">
+        <v>1198438</v>
+      </c>
+      <c r="BP6">
+        <v>476488</v>
+      </c>
+      <c r="BQ6">
+        <v>486388</v>
+      </c>
+      <c r="BR6">
+        <v>459753</v>
+      </c>
+      <c r="BS6">
+        <v>993420</v>
+      </c>
+      <c r="BT6">
+        <v>850525</v>
+      </c>
+      <c r="BU6">
+        <v>601642</v>
+      </c>
+      <c r="BV6">
+        <v>528351</v>
+      </c>
+      <c r="BW6">
+        <v>461829</v>
+      </c>
+      <c r="BX6">
+        <v>726551</v>
+      </c>
+      <c r="BY6">
+        <v>1072591</v>
+      </c>
+      <c r="BZ6">
+        <v>551189</v>
+      </c>
+      <c r="CA6">
+        <v>327997</v>
+      </c>
+    </row>
+    <row r="7" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>2012</v>
+      </c>
+      <c r="B7">
+        <v>64075986</v>
+      </c>
+      <c r="C7">
+        <v>5674843</v>
+      </c>
+      <c r="D7">
+        <v>1122627</v>
+      </c>
+      <c r="E7">
+        <v>787653</v>
+      </c>
+      <c r="F7">
+        <v>1010898</v>
+      </c>
+      <c r="G7">
+        <v>620454</v>
+      </c>
+      <c r="H7">
+        <v>284061</v>
+      </c>
+      <c r="I7">
+        <v>333256</v>
+      </c>
+      <c r="J7">
+        <v>756127</v>
+      </c>
+      <c r="K7">
+        <v>213587</v>
+      </c>
+      <c r="L7">
+        <v>679370</v>
+      </c>
+      <c r="M7">
+        <v>253831</v>
+      </c>
+      <c r="N7">
+        <v>469652</v>
+      </c>
+      <c r="O7">
+        <v>545596</v>
+      </c>
+      <c r="P7">
+        <v>1203223</v>
+      </c>
+      <c r="Q7">
+        <v>838914</v>
+      </c>
+      <c r="R7">
+        <v>866064</v>
+      </c>
+      <c r="S7">
+        <v>842684</v>
+      </c>
+      <c r="T7">
+        <v>845053</v>
+      </c>
+      <c r="U7">
+        <v>466079</v>
+      </c>
+      <c r="V7">
+        <v>512568</v>
+      </c>
+      <c r="W7">
+        <v>499098</v>
+      </c>
+      <c r="X7">
+        <v>194086</v>
+      </c>
+      <c r="Y7">
+        <v>516855</v>
+      </c>
+      <c r="Z7">
+        <v>1338656</v>
+      </c>
+      <c r="AA7">
+        <v>637736</v>
+      </c>
+      <c r="AB7">
+        <v>222013</v>
+      </c>
+      <c r="AC7">
+        <v>492182</v>
+      </c>
+      <c r="AD7">
+        <v>1526071</v>
+      </c>
+      <c r="AE7">
+        <v>511016</v>
+      </c>
+      <c r="AF7">
+        <v>1012064</v>
+      </c>
+      <c r="AG7">
+        <v>438039</v>
+      </c>
+      <c r="AH7">
+        <v>254931</v>
+      </c>
+      <c r="AI7">
+        <v>353847</v>
+      </c>
+      <c r="AJ7">
+        <v>183849</v>
+      </c>
+      <c r="AK7">
+        <v>626708</v>
+      </c>
+      <c r="AL7">
+        <v>747372</v>
+      </c>
+      <c r="AM7">
+        <v>663485</v>
+      </c>
+      <c r="AN7">
+        <v>301467</v>
+      </c>
+      <c r="AO7">
+        <v>1367010</v>
+      </c>
+      <c r="AP7">
+        <v>493767</v>
+      </c>
+      <c r="AQ7">
+        <v>407634</v>
+      </c>
+      <c r="AR7">
+        <v>624920</v>
+      </c>
+      <c r="AS7">
+        <v>502551</v>
+      </c>
+      <c r="AT7">
+        <v>509870</v>
+      </c>
+      <c r="AU7">
+        <v>1548107</v>
+      </c>
+      <c r="AV7">
+        <v>340581</v>
+      </c>
+      <c r="AW7">
+        <v>704768</v>
+      </c>
+      <c r="AX7">
+        <v>1123351</v>
+      </c>
+      <c r="AY7">
+        <v>981655</v>
+      </c>
+      <c r="AZ7">
+        <v>1766066</v>
+      </c>
+      <c r="BA7">
+        <v>939736</v>
+      </c>
+      <c r="BB7">
+        <v>1305058</v>
+      </c>
+      <c r="BC7">
+        <v>372241</v>
+      </c>
+      <c r="BD7">
+        <v>1452203</v>
+      </c>
+      <c r="BE7">
+        <v>1816057</v>
+      </c>
+      <c r="BF7">
+        <v>538853</v>
+      </c>
+      <c r="BG7">
+        <v>1559085</v>
+      </c>
+      <c r="BH7">
+        <v>1127423</v>
+      </c>
+      <c r="BI7">
+        <v>2585325</v>
+      </c>
+      <c r="BJ7">
+        <v>1380399</v>
+      </c>
+      <c r="BK7">
+        <v>1646144</v>
+      </c>
+      <c r="BL7">
+        <v>757534</v>
+      </c>
+      <c r="BM7">
+        <v>403952</v>
+      </c>
+      <c r="BN7">
+        <v>244048</v>
+      </c>
+      <c r="BO7">
+        <v>1198656</v>
+      </c>
+      <c r="BP7">
+        <v>476612</v>
+      </c>
+      <c r="BQ7">
+        <v>486472</v>
+      </c>
+      <c r="BR7">
+        <v>458750</v>
+      </c>
+      <c r="BS7">
+        <v>990807</v>
+      </c>
+      <c r="BT7">
+        <v>851357</v>
+      </c>
+      <c r="BU7">
+        <v>601504</v>
+      </c>
+      <c r="BV7">
+        <v>531018</v>
+      </c>
+      <c r="BW7">
+        <v>461040</v>
+      </c>
+      <c r="BX7">
+        <v>726009</v>
+      </c>
+      <c r="BY7">
+        <v>1071686</v>
+      </c>
+      <c r="BZ7">
+        <v>549688</v>
+      </c>
+      <c r="CA7">
+        <v>328034</v>
+      </c>
+    </row>
+    <row r="8" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>2013</v>
+      </c>
+      <c r="B8">
+        <v>64076033</v>
+      </c>
+      <c r="C8">
+        <v>5674843</v>
+      </c>
+      <c r="D8">
+        <v>1122627</v>
+      </c>
+      <c r="E8">
+        <v>787653</v>
+      </c>
+      <c r="F8">
+        <v>1010898</v>
+      </c>
+      <c r="G8">
+        <v>620454</v>
+      </c>
+      <c r="H8">
+        <v>284061</v>
+      </c>
+      <c r="I8">
+        <v>333256</v>
+      </c>
+      <c r="J8">
+        <v>756127</v>
+      </c>
+      <c r="K8">
+        <v>213587</v>
+      </c>
+      <c r="L8">
+        <v>679370</v>
+      </c>
+      <c r="M8">
+        <v>253831</v>
+      </c>
+      <c r="N8">
+        <v>469652</v>
+      </c>
+      <c r="O8">
+        <v>545596</v>
+      </c>
+      <c r="P8">
+        <v>1203223</v>
+      </c>
+      <c r="Q8">
+        <v>838914</v>
+      </c>
+      <c r="R8">
+        <v>866064</v>
+      </c>
+      <c r="S8">
+        <v>842684</v>
+      </c>
+      <c r="T8">
+        <v>845053</v>
+      </c>
+      <c r="U8">
+        <v>466079</v>
+      </c>
+      <c r="V8">
+        <v>512568</v>
+      </c>
+      <c r="W8">
+        <v>499098</v>
+      </c>
+      <c r="X8">
+        <v>194086</v>
+      </c>
+      <c r="Y8">
+        <v>516855</v>
+      </c>
+      <c r="Z8">
+        <v>1338656</v>
+      </c>
+      <c r="AA8">
+        <v>637736</v>
+      </c>
+      <c r="AB8">
+        <v>222013</v>
+      </c>
+      <c r="AC8">
+        <v>492182</v>
+      </c>
+      <c r="AD8">
+        <v>1526071</v>
+      </c>
+      <c r="AE8">
+        <v>511063</v>
+      </c>
+      <c r="AF8">
+        <v>1012064</v>
+      </c>
+      <c r="AG8">
+        <v>438039</v>
+      </c>
+      <c r="AH8">
+        <v>254931</v>
+      </c>
+      <c r="AI8">
+        <v>353847</v>
+      </c>
+      <c r="AJ8">
+        <v>183849</v>
+      </c>
+      <c r="AK8">
+        <v>626708</v>
+      </c>
+      <c r="AL8">
+        <v>747372</v>
+      </c>
+      <c r="AM8">
+        <v>663485</v>
+      </c>
+      <c r="AN8">
+        <v>301467</v>
+      </c>
+      <c r="AO8">
+        <v>1367010</v>
+      </c>
+      <c r="AP8">
+        <v>493767</v>
+      </c>
+      <c r="AQ8">
+        <v>407634</v>
+      </c>
+      <c r="AR8">
+        <v>624920</v>
+      </c>
+      <c r="AS8">
+        <v>502551</v>
+      </c>
+      <c r="AT8">
+        <v>509870</v>
+      </c>
+      <c r="AU8">
+        <v>1548107</v>
+      </c>
+      <c r="AV8">
+        <v>340581</v>
+      </c>
+      <c r="AW8">
+        <v>704768</v>
+      </c>
+      <c r="AX8">
+        <v>1123351</v>
+      </c>
+      <c r="AY8">
+        <v>981655</v>
+      </c>
+      <c r="AZ8">
+        <v>1766066</v>
+      </c>
+      <c r="BA8">
+        <v>939736</v>
+      </c>
+      <c r="BB8">
+        <v>1305058</v>
+      </c>
+      <c r="BC8">
+        <v>372241</v>
+      </c>
+      <c r="BD8">
+        <v>1452203</v>
+      </c>
+      <c r="BE8">
+        <v>1816057</v>
+      </c>
+      <c r="BF8">
+        <v>538853</v>
+      </c>
+      <c r="BG8">
+        <v>1559085</v>
+      </c>
+      <c r="BH8">
+        <v>1127423</v>
+      </c>
+      <c r="BI8">
+        <v>2585325</v>
+      </c>
+      <c r="BJ8">
+        <v>1380399</v>
+      </c>
+      <c r="BK8">
+        <v>1646144</v>
+      </c>
+      <c r="BL8">
+        <v>757534</v>
+      </c>
+      <c r="BM8">
+        <v>403952</v>
+      </c>
+      <c r="BN8">
+        <v>244048</v>
+      </c>
+      <c r="BO8">
+        <v>1198656</v>
+      </c>
+      <c r="BP8">
+        <v>476612</v>
+      </c>
+      <c r="BQ8">
+        <v>486472</v>
+      </c>
+      <c r="BR8">
+        <v>458750</v>
+      </c>
+      <c r="BS8">
+        <v>990807</v>
+      </c>
+      <c r="BT8">
+        <v>851357</v>
+      </c>
+      <c r="BU8">
+        <v>601504</v>
+      </c>
+      <c r="BV8">
+        <v>531018</v>
+      </c>
+      <c r="BW8">
+        <v>461040</v>
+      </c>
+      <c r="BX8">
+        <v>726009</v>
+      </c>
+      <c r="BY8">
+        <v>1071686</v>
+      </c>
+      <c r="BZ8">
+        <v>549688</v>
+      </c>
+      <c r="CA8">
+        <v>328034</v>
+      </c>
+    </row>
+    <row r="9" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>2014</v>
+      </c>
+      <c r="B9">
+        <v>64955313</v>
+      </c>
+      <c r="C9">
+        <v>5689268</v>
+      </c>
+      <c r="D9">
+        <v>1165070</v>
+      </c>
+      <c r="E9">
+        <v>800785</v>
+      </c>
+      <c r="F9">
+        <v>1063608</v>
+      </c>
+      <c r="G9">
+        <v>631338</v>
+      </c>
+      <c r="H9">
+        <v>283650</v>
+      </c>
+      <c r="I9">
+        <v>332526</v>
+      </c>
+      <c r="J9">
+        <v>758188</v>
+      </c>
+      <c r="K9">
+        <v>212424</v>
+      </c>
+      <c r="L9">
+        <v>692852</v>
+      </c>
+      <c r="M9">
+        <v>256693</v>
+      </c>
+      <c r="N9">
+        <v>477741</v>
+      </c>
+      <c r="O9">
+        <v>551562</v>
+      </c>
+      <c r="P9">
+        <v>1251570</v>
+      </c>
+      <c r="Q9">
+        <v>845540</v>
+      </c>
+      <c r="R9">
+        <v>886627</v>
+      </c>
+      <c r="S9">
+        <v>851689</v>
+      </c>
+      <c r="T9">
+        <v>848559</v>
+      </c>
+      <c r="U9">
+        <v>472640</v>
+      </c>
+      <c r="V9">
+        <v>522689</v>
+      </c>
+      <c r="W9">
+        <v>525672</v>
+      </c>
+      <c r="X9">
+        <v>194153</v>
+      </c>
+      <c r="Y9">
+        <v>525805</v>
+      </c>
+      <c r="Z9">
+        <v>1405889</v>
+      </c>
+      <c r="AA9">
+        <v>667806</v>
+      </c>
+      <c r="AB9">
+        <v>224370</v>
+      </c>
+      <c r="AC9">
+        <v>499435</v>
+      </c>
+      <c r="AD9">
+        <v>1544936</v>
+      </c>
+      <c r="AE9">
+        <v>519220</v>
+      </c>
+      <c r="AF9">
+        <v>1036021</v>
+      </c>
+      <c r="AG9">
+        <v>453850</v>
+      </c>
+      <c r="AH9">
+        <v>260395</v>
+      </c>
+      <c r="AI9">
+        <v>373943</v>
+      </c>
+      <c r="AJ9">
+        <v>175933</v>
+      </c>
+      <c r="AK9">
+        <v>637395</v>
+      </c>
+      <c r="AL9">
+        <v>770472</v>
+      </c>
+      <c r="AM9">
+        <v>682512</v>
+      </c>
+      <c r="AN9">
+        <v>311233</v>
+      </c>
+      <c r="AO9">
+        <v>1395596</v>
+      </c>
+      <c r="AP9">
+        <v>509025</v>
+      </c>
+      <c r="AQ9">
+        <v>417401</v>
+      </c>
+      <c r="AR9">
+        <v>633359</v>
+      </c>
+      <c r="AS9">
+        <v>508001</v>
+      </c>
+      <c r="AT9">
+        <v>516101</v>
+      </c>
+      <c r="AU9">
+        <v>1567132</v>
+      </c>
+      <c r="AV9">
+        <v>345159</v>
+      </c>
+      <c r="AW9">
+        <v>712101</v>
+      </c>
+      <c r="AX9">
+        <v>1136466</v>
+      </c>
+      <c r="AY9">
+        <v>984468</v>
+      </c>
+      <c r="AZ9">
+        <v>1785852</v>
+      </c>
+      <c r="BA9">
+        <v>958116</v>
+      </c>
+      <c r="BB9">
+        <v>1308638</v>
+      </c>
+      <c r="BC9">
+        <v>375039</v>
+      </c>
+      <c r="BD9">
+        <v>1463620</v>
+      </c>
+      <c r="BE9">
+        <v>1840596</v>
+      </c>
+      <c r="BF9">
+        <v>540297</v>
+      </c>
+      <c r="BG9">
+        <v>1576343</v>
+      </c>
+      <c r="BH9">
+        <v>1136386</v>
+      </c>
+      <c r="BI9">
+        <v>2615340</v>
+      </c>
+      <c r="BJ9">
+        <v>1389915</v>
+      </c>
+      <c r="BK9">
+        <v>1672586</v>
+      </c>
+      <c r="BL9">
+        <v>753937</v>
+      </c>
+      <c r="BM9">
+        <v>405368</v>
+      </c>
+      <c r="BN9">
+        <v>247364</v>
+      </c>
+      <c r="BO9">
+        <v>1206180</v>
+      </c>
+      <c r="BP9">
+        <v>478088</v>
+      </c>
+      <c r="BQ9">
+        <v>485599</v>
+      </c>
+      <c r="BR9">
+        <v>455078</v>
+      </c>
+      <c r="BS9">
+        <v>995102</v>
+      </c>
+      <c r="BT9">
+        <v>857682</v>
+      </c>
+      <c r="BU9">
+        <v>602586</v>
+      </c>
+      <c r="BV9">
+        <v>535953</v>
+      </c>
+      <c r="BW9">
+        <v>460698</v>
+      </c>
+      <c r="BX9">
+        <v>729076</v>
+      </c>
+      <c r="BY9">
+        <v>1072949</v>
+      </c>
+      <c r="BZ9">
+        <v>548199</v>
+      </c>
+      <c r="CA9">
+        <v>329858</v>
+      </c>
+    </row>
+    <row r="10" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>2015</v>
+      </c>
+      <c r="B10">
+        <v>65124716</v>
+      </c>
+      <c r="C10">
+        <v>5692284</v>
+      </c>
+      <c r="D10">
+        <v>1173870</v>
+      </c>
+      <c r="E10">
+        <v>803599</v>
+      </c>
+      <c r="F10">
+        <v>1074058</v>
+      </c>
+      <c r="G10">
+        <v>633460</v>
+      </c>
+      <c r="H10">
+        <v>283568</v>
+      </c>
+      <c r="I10">
+        <v>332283</v>
+      </c>
+      <c r="J10">
+        <v>758406</v>
+      </c>
+      <c r="K10">
+        <v>212158</v>
+      </c>
+      <c r="L10">
+        <v>695478</v>
+      </c>
+      <c r="M10">
+        <v>257300</v>
+      </c>
+      <c r="N10">
+        <v>479314</v>
+      </c>
+      <c r="O10">
+        <v>552187</v>
+      </c>
+      <c r="P10">
+        <v>1261530</v>
+      </c>
+      <c r="Q10">
+        <v>848198</v>
+      </c>
+      <c r="R10">
+        <v>891071</v>
+      </c>
+      <c r="S10">
+        <v>853217</v>
+      </c>
+      <c r="T10">
+        <v>849053</v>
+      </c>
+      <c r="U10">
+        <v>474192</v>
+      </c>
+      <c r="V10">
+        <v>525107</v>
+      </c>
+      <c r="W10">
+        <v>531887</v>
+      </c>
+      <c r="X10">
+        <v>194189</v>
+      </c>
+      <c r="Y10">
+        <v>527350</v>
+      </c>
+      <c r="Z10">
+        <v>1421425</v>
+      </c>
+      <c r="AA10">
+        <v>674393</v>
+      </c>
+      <c r="AB10">
+        <v>224730</v>
+      </c>
+      <c r="AC10">
+        <v>500575</v>
+      </c>
+      <c r="AD10">
+        <v>1548028</v>
+      </c>
+      <c r="AE10">
+        <v>520419</v>
+      </c>
+      <c r="AF10">
+        <v>1040230</v>
+      </c>
+      <c r="AG10">
+        <v>456811</v>
+      </c>
+      <c r="AH10">
+        <v>261370</v>
+      </c>
+      <c r="AI10">
+        <v>378364</v>
+      </c>
+      <c r="AJ10">
+        <v>177089</v>
+      </c>
+      <c r="AK10">
+        <v>638746</v>
+      </c>
+      <c r="AL10">
+        <v>774799</v>
+      </c>
+      <c r="AM10">
+        <v>686186</v>
+      </c>
+      <c r="AN10">
+        <v>312673</v>
+      </c>
+      <c r="AO10">
+        <v>1401303</v>
+      </c>
+      <c r="AP10">
+        <v>511911</v>
+      </c>
+      <c r="AQ10">
+        <v>418566</v>
+      </c>
+      <c r="AR10">
+        <v>634513</v>
+      </c>
+      <c r="AS10">
+        <v>508864</v>
+      </c>
+      <c r="AT10">
+        <v>517260</v>
+      </c>
+      <c r="AU10">
+        <v>1570300</v>
+      </c>
+      <c r="AV10">
+        <v>346016</v>
+      </c>
+      <c r="AW10">
+        <v>713341</v>
+      </c>
+      <c r="AX10">
+        <v>1138609</v>
+      </c>
+      <c r="AY10">
+        <v>984907</v>
+      </c>
+      <c r="AZ10">
+        <v>1790049</v>
+      </c>
+      <c r="BA10">
+        <v>960588</v>
+      </c>
+      <c r="BB10">
+        <v>1308318</v>
+      </c>
+      <c r="BC10">
+        <v>375380</v>
+      </c>
+      <c r="BD10">
+        <v>1465213</v>
+      </c>
+      <c r="BE10">
+        <v>1844669</v>
+      </c>
+      <c r="BF10">
+        <v>540211</v>
+      </c>
+      <c r="BG10">
+        <v>1579248</v>
+      </c>
+      <c r="BH10">
+        <v>1137049</v>
+      </c>
+      <c r="BI10">
+        <v>2620517</v>
+      </c>
+      <c r="BJ10">
+        <v>1391636</v>
+      </c>
+      <c r="BK10">
+        <v>1678284</v>
+      </c>
+      <c r="BL10">
+        <v>753013</v>
+      </c>
+      <c r="BM10">
+        <v>405468</v>
+      </c>
+      <c r="BN10">
+        <v>248178</v>
+      </c>
+      <c r="BO10">
+        <v>1207699</v>
+      </c>
+      <c r="BP10">
+        <v>478264</v>
+      </c>
+      <c r="BQ10">
+        <v>484454</v>
+      </c>
+      <c r="BR10">
+        <v>454083</v>
+      </c>
+      <c r="BS10">
+        <v>995807</v>
+      </c>
+      <c r="BT10">
+        <v>858988</v>
+      </c>
+      <c r="BU10">
+        <v>602460</v>
+      </c>
+      <c r="BV10">
+        <v>539553</v>
+      </c>
+      <c r="BW10">
+        <v>460400</v>
+      </c>
+      <c r="BX10">
+        <v>729522</v>
+      </c>
+      <c r="BY10">
+        <v>1072756</v>
+      </c>
+      <c r="BZ10">
+        <v>547543</v>
+      </c>
+      <c r="CA10">
+        <v>330179</v>
+      </c>
+    </row>
+    <row r="11" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>2016</v>
+      </c>
+      <c r="B11">
+        <v>65426907</v>
+      </c>
+      <c r="C11">
+        <v>5694347</v>
+      </c>
+      <c r="D11">
+        <v>1183791</v>
+      </c>
+      <c r="E11">
+        <v>805980</v>
+      </c>
+      <c r="F11">
+        <v>1084154</v>
+      </c>
+      <c r="G11">
+        <v>635567</v>
+      </c>
+      <c r="H11">
+        <v>283371</v>
+      </c>
+      <c r="I11">
+        <v>331968</v>
+      </c>
+      <c r="J11">
+        <v>758531</v>
+      </c>
+      <c r="K11">
+        <v>211792</v>
+      </c>
+      <c r="L11">
+        <v>698190</v>
+      </c>
+      <c r="M11">
+        <v>257939</v>
+      </c>
+      <c r="N11">
+        <v>480755</v>
+      </c>
+      <c r="O11">
+        <v>554555</v>
+      </c>
+      <c r="P11">
+        <v>1270420</v>
+      </c>
+      <c r="Q11">
+        <v>865172</v>
+      </c>
+      <c r="R11">
+        <v>895207</v>
+      </c>
+      <c r="S11">
+        <v>860549</v>
+      </c>
+      <c r="T11">
+        <v>849376</v>
+      </c>
+      <c r="U11">
+        <v>476391</v>
+      </c>
+      <c r="V11">
+        <v>529912</v>
+      </c>
+      <c r="W11">
+        <v>538671</v>
+      </c>
+      <c r="X11">
+        <v>194283</v>
+      </c>
+      <c r="Y11">
+        <v>529194</v>
+      </c>
+      <c r="Z11">
+        <v>1438231</v>
+      </c>
+      <c r="AA11">
+        <v>681696</v>
+      </c>
+      <c r="AB11">
+        <v>227083</v>
+      </c>
+      <c r="AC11">
+        <v>503203</v>
+      </c>
+      <c r="AD11">
+        <v>1550278</v>
+      </c>
+      <c r="AE11">
+        <v>521570</v>
+      </c>
+      <c r="AF11">
+        <v>1043501</v>
+      </c>
+      <c r="AG11">
+        <v>459456</v>
+      </c>
+      <c r="AH11">
+        <v>262721</v>
+      </c>
+      <c r="AI11">
+        <v>382485</v>
+      </c>
+      <c r="AJ11">
+        <v>182313</v>
+      </c>
+      <c r="AK11">
+        <v>639770</v>
+      </c>
+      <c r="AL11">
+        <v>778941</v>
+      </c>
+      <c r="AM11">
+        <v>690104</v>
+      </c>
+      <c r="AN11">
+        <v>314297</v>
+      </c>
+      <c r="AO11">
+        <v>1405939</v>
+      </c>
+      <c r="AP11">
+        <v>515025</v>
+      </c>
+      <c r="AQ11">
+        <v>419607</v>
+      </c>
+      <c r="AR11">
+        <v>636666</v>
+      </c>
+      <c r="AS11">
+        <v>509469</v>
+      </c>
+      <c r="AT11">
+        <v>518420</v>
+      </c>
+      <c r="AU11">
+        <v>1572726</v>
+      </c>
+      <c r="AV11">
+        <v>347059</v>
+      </c>
+      <c r="AW11">
+        <v>714369</v>
+      </c>
+      <c r="AX11">
+        <v>1140673</v>
+      </c>
+      <c r="AY11">
+        <v>985055</v>
+      </c>
+      <c r="AZ11">
+        <v>1794032</v>
+      </c>
+      <c r="BA11">
+        <v>962592</v>
+      </c>
+      <c r="BB11">
+        <v>1308241</v>
+      </c>
+      <c r="BC11">
+        <v>375881</v>
+      </c>
+      <c r="BD11">
+        <v>1467006</v>
+      </c>
+      <c r="BE11">
+        <v>1851049</v>
+      </c>
+      <c r="BF11">
+        <v>540197</v>
+      </c>
+      <c r="BG11">
+        <v>1581955</v>
+      </c>
+      <c r="BH11">
+        <v>1137651</v>
+      </c>
+      <c r="BI11">
+        <v>2624668</v>
+      </c>
+      <c r="BJ11">
+        <v>1393330</v>
+      </c>
+      <c r="BK11">
+        <v>1703263</v>
+      </c>
+      <c r="BL11">
+        <v>752685</v>
+      </c>
+      <c r="BM11">
+        <v>405927</v>
+      </c>
+      <c r="BN11">
+        <v>260971</v>
+      </c>
+      <c r="BO11">
+        <v>1242825</v>
+      </c>
+      <c r="BP11">
+        <v>478890</v>
+      </c>
+      <c r="BQ11">
+        <v>483550</v>
+      </c>
+      <c r="BR11">
+        <v>453213</v>
+      </c>
+      <c r="BS11">
+        <v>996397</v>
+      </c>
+      <c r="BT11">
+        <v>861194</v>
+      </c>
+      <c r="BU11">
+        <v>602085</v>
+      </c>
+      <c r="BV11">
+        <v>578968</v>
+      </c>
+      <c r="BW11">
+        <v>460084</v>
+      </c>
+      <c r="BX11">
+        <v>729839</v>
+      </c>
+      <c r="BY11">
+        <v>1072349</v>
+      </c>
+      <c r="BZ11">
+        <v>546750</v>
+      </c>
+      <c r="CA11">
+        <v>330543</v>
+      </c>
+    </row>
+    <row r="12" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>2017</v>
+      </c>
+      <c r="B12">
+        <v>66060027</v>
+      </c>
+      <c r="C12">
+        <v>5684531</v>
+      </c>
+      <c r="D12">
+        <v>1220829</v>
+      </c>
+      <c r="E12">
+        <v>812086</v>
+      </c>
+      <c r="F12">
+        <v>1120246</v>
+      </c>
+      <c r="G12">
+        <v>641052</v>
+      </c>
+      <c r="H12">
+        <v>281796</v>
+      </c>
+      <c r="I12">
+        <v>330077</v>
+      </c>
+      <c r="J12">
+        <v>757296</v>
+      </c>
+      <c r="K12">
+        <v>210337</v>
+      </c>
+      <c r="L12">
+        <v>707145</v>
+      </c>
+      <c r="M12">
+        <v>258850</v>
+      </c>
+      <c r="N12">
+        <v>486187</v>
+      </c>
+      <c r="O12">
+        <v>560478</v>
+      </c>
+      <c r="P12">
+        <v>1302160</v>
+      </c>
+      <c r="Q12">
+        <v>886546</v>
+      </c>
+      <c r="R12">
+        <v>908249</v>
+      </c>
+      <c r="S12">
+        <v>870769</v>
+      </c>
+      <c r="T12">
+        <v>850285</v>
+      </c>
+      <c r="U12">
+        <v>481514</v>
+      </c>
+      <c r="V12">
+        <v>541756</v>
+      </c>
+      <c r="W12">
+        <v>562592</v>
+      </c>
+      <c r="X12">
+        <v>193985</v>
+      </c>
+      <c r="Y12">
+        <v>533463</v>
+      </c>
+      <c r="Z12">
+        <v>1496086</v>
+      </c>
+      <c r="AA12">
+        <v>705729</v>
+      </c>
+      <c r="AB12">
+        <v>229542</v>
+      </c>
+      <c r="AC12">
+        <v>508627</v>
+      </c>
+      <c r="AD12">
+        <v>1555957</v>
+      </c>
+      <c r="AE12">
+        <v>524291</v>
+      </c>
+      <c r="AF12">
+        <v>1054247</v>
+      </c>
+      <c r="AG12">
+        <v>467851</v>
+      </c>
+      <c r="AH12">
+        <v>266535</v>
+      </c>
+      <c r="AI12">
+        <v>398092</v>
+      </c>
+      <c r="AJ12">
+        <v>189777</v>
+      </c>
+      <c r="AK12">
+        <v>642377</v>
+      </c>
+      <c r="AL12">
+        <v>792961</v>
+      </c>
+      <c r="AM12">
+        <v>705379</v>
+      </c>
+      <c r="AN12">
+        <v>318655</v>
+      </c>
+      <c r="AO12">
+        <v>1420834</v>
+      </c>
+      <c r="AP12">
+        <v>524788</v>
+      </c>
+      <c r="AQ12">
+        <v>422328</v>
+      </c>
+      <c r="AR12">
+        <v>640734</v>
+      </c>
+      <c r="AS12">
+        <v>511188</v>
+      </c>
+      <c r="AT12">
+        <v>521125</v>
+      </c>
+      <c r="AU12">
+        <v>1580937</v>
+      </c>
+      <c r="AV12">
+        <v>350128</v>
+      </c>
+      <c r="AW12">
+        <v>717451</v>
+      </c>
+      <c r="AX12">
+        <v>1147710</v>
+      </c>
+      <c r="AY12">
+        <v>985619</v>
+      </c>
+      <c r="AZ12">
+        <v>1803831</v>
+      </c>
+      <c r="BA12">
+        <v>963277</v>
+      </c>
+      <c r="BB12">
+        <v>1307947</v>
+      </c>
+      <c r="BC12">
+        <v>377614</v>
+      </c>
+      <c r="BD12">
+        <v>1471185</v>
+      </c>
+      <c r="BE12">
+        <v>1866299</v>
+      </c>
+      <c r="BF12">
+        <v>539679</v>
+      </c>
+      <c r="BG12">
+        <v>1589900</v>
+      </c>
+      <c r="BH12">
+        <v>1138778</v>
+      </c>
+      <c r="BI12">
+        <v>2635331</v>
+      </c>
+      <c r="BJ12">
+        <v>1396374</v>
+      </c>
+      <c r="BK12">
+        <v>1741301</v>
+      </c>
+      <c r="BL12">
+        <v>747699</v>
+      </c>
+      <c r="BM12">
+        <v>405959</v>
+      </c>
+      <c r="BN12">
+        <v>277486</v>
+      </c>
+      <c r="BO12">
+        <v>1285080</v>
+      </c>
+      <c r="BP12">
+        <v>479877</v>
+      </c>
+      <c r="BQ12">
+        <v>478144</v>
+      </c>
+      <c r="BR12">
+        <v>448686</v>
+      </c>
+      <c r="BS12">
+        <v>995277</v>
+      </c>
+      <c r="BT12">
+        <v>865564</v>
+      </c>
+      <c r="BU12">
+        <v>599775</v>
+      </c>
+      <c r="BV12">
+        <v>638115</v>
+      </c>
+      <c r="BW12">
+        <v>457645</v>
+      </c>
+      <c r="BX12">
+        <v>729337</v>
+      </c>
+      <c r="BY12">
+        <v>1065895</v>
+      </c>
+      <c r="BZ12">
+        <v>542674</v>
+      </c>
+      <c r="CA12">
+        <v>330121</v>
+      </c>
+    </row>
+    <row r="13" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>2018</v>
+      </c>
+      <c r="B13">
+        <v>66301242</v>
+      </c>
+      <c r="C13">
+        <v>5679532</v>
+      </c>
+      <c r="D13">
+        <v>1238015</v>
+      </c>
+      <c r="E13">
+        <v>815647</v>
+      </c>
+      <c r="F13">
+        <v>1137603</v>
+      </c>
+      <c r="G13">
+        <v>643531</v>
+      </c>
+      <c r="H13">
+        <v>281014</v>
+      </c>
+      <c r="I13">
+        <v>328993</v>
+      </c>
+      <c r="J13">
+        <v>758003</v>
+      </c>
+      <c r="K13">
+        <v>209733</v>
+      </c>
+      <c r="L13">
+        <v>712449</v>
+      </c>
+      <c r="M13">
+        <v>259718</v>
+      </c>
+      <c r="N13">
+        <v>489592</v>
+      </c>
+      <c r="O13">
+        <v>563014</v>
+      </c>
+      <c r="P13">
+        <v>1318687</v>
+      </c>
+      <c r="Q13">
+        <v>890565</v>
+      </c>
+      <c r="R13">
+        <v>914273</v>
+      </c>
+      <c r="S13">
+        <v>872615</v>
+      </c>
+      <c r="T13">
+        <v>850362</v>
+      </c>
+      <c r="U13">
+        <v>483335</v>
+      </c>
+      <c r="V13">
+        <v>546396</v>
+      </c>
+      <c r="W13">
+        <v>573215</v>
+      </c>
+      <c r="X13">
+        <v>193847</v>
+      </c>
+      <c r="Y13">
+        <v>535478</v>
+      </c>
+      <c r="Z13">
+        <v>1522285</v>
+      </c>
+      <c r="AA13">
+        <v>717276</v>
+      </c>
+      <c r="AB13">
+        <v>229782</v>
+      </c>
+      <c r="AC13">
+        <v>510307</v>
+      </c>
+      <c r="AD13">
+        <v>1558958</v>
+      </c>
+      <c r="AE13">
+        <v>524951</v>
+      </c>
+      <c r="AF13">
+        <v>1060541</v>
+      </c>
+      <c r="AG13">
+        <v>471754</v>
+      </c>
+      <c r="AH13">
+        <v>267866</v>
+      </c>
+      <c r="AI13">
+        <v>406113</v>
+      </c>
+      <c r="AJ13">
+        <v>191134</v>
+      </c>
+      <c r="AK13">
+        <v>643093</v>
+      </c>
+      <c r="AL13">
+        <v>799357</v>
+      </c>
+      <c r="AM13">
+        <v>713937</v>
+      </c>
+      <c r="AN13">
+        <v>320637</v>
+      </c>
+      <c r="AO13">
+        <v>1428429</v>
+      </c>
+      <c r="AP13">
+        <v>529811</v>
+      </c>
+      <c r="AQ13">
+        <v>423485</v>
+      </c>
+      <c r="AR13">
+        <v>642220</v>
+      </c>
+      <c r="AS13">
+        <v>511878</v>
+      </c>
+      <c r="AT13">
+        <v>521995</v>
+      </c>
+      <c r="AU13">
+        <v>1584878</v>
+      </c>
+      <c r="AV13">
+        <v>351532</v>
+      </c>
+      <c r="AW13">
+        <v>718406</v>
+      </c>
+      <c r="AX13">
+        <v>1150876</v>
+      </c>
+      <c r="AY13">
+        <v>985676</v>
+      </c>
+      <c r="AZ13">
+        <v>1805903</v>
+      </c>
+      <c r="BA13">
+        <v>963060</v>
+      </c>
+      <c r="BB13">
+        <v>1307560</v>
+      </c>
+      <c r="BC13">
+        <v>378363</v>
+      </c>
+      <c r="BD13">
+        <v>1472521</v>
+      </c>
+      <c r="BE13">
+        <v>1872091</v>
+      </c>
+      <c r="BF13">
+        <v>539136</v>
+      </c>
+      <c r="BG13">
+        <v>1593378</v>
+      </c>
+      <c r="BH13">
+        <v>1139067</v>
+      </c>
+      <c r="BI13">
+        <v>2642815</v>
+      </c>
+      <c r="BJ13">
+        <v>1397519</v>
+      </c>
+      <c r="BK13">
+        <v>1755291</v>
+      </c>
+      <c r="BL13">
+        <v>744714</v>
+      </c>
+      <c r="BM13">
+        <v>405936</v>
+      </c>
+      <c r="BN13">
+        <v>280826</v>
+      </c>
+      <c r="BO13">
+        <v>1289873</v>
+      </c>
+      <c r="BP13">
+        <v>479414</v>
+      </c>
+      <c r="BQ13">
+        <v>476157</v>
+      </c>
+      <c r="BR13">
+        <v>446326</v>
+      </c>
+      <c r="BS13">
+        <v>994936</v>
+      </c>
+      <c r="BT13">
+        <v>866129</v>
+      </c>
+      <c r="BU13">
+        <v>598287</v>
+      </c>
+      <c r="BV13">
+        <v>649472</v>
+      </c>
+      <c r="BW13">
+        <v>456247</v>
+      </c>
+      <c r="BX13">
+        <v>728470</v>
+      </c>
+      <c r="BY13">
+        <v>1064649</v>
+      </c>
+      <c r="BZ13">
+        <v>540620</v>
+      </c>
+      <c r="CA13">
+        <v>329688</v>
+      </c>
+    </row>
+    <row r="14" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>2019</v>
+      </c>
+      <c r="B14">
+        <v>66486458</v>
+      </c>
+      <c r="C14">
+        <v>5671457</v>
+      </c>
+      <c r="D14">
+        <v>1255840</v>
+      </c>
+      <c r="E14">
+        <v>818815</v>
+      </c>
+      <c r="F14">
+        <v>1154848</v>
+      </c>
+      <c r="G14">
+        <v>645468</v>
+      </c>
+      <c r="H14">
+        <v>280246</v>
+      </c>
+      <c r="I14">
+        <v>327437</v>
+      </c>
+      <c r="J14">
+        <v>757145</v>
+      </c>
+      <c r="K14">
+        <v>208912</v>
+      </c>
+      <c r="L14">
+        <v>717561</v>
+      </c>
+      <c r="M14">
+        <v>260421</v>
+      </c>
+      <c r="N14">
+        <v>493159</v>
+      </c>
+      <c r="O14">
+        <v>565198</v>
+      </c>
+      <c r="P14">
+        <v>1335742</v>
+      </c>
+      <c r="Q14">
+        <v>894338</v>
+      </c>
+      <c r="R14">
+        <v>918542</v>
+      </c>
+      <c r="S14">
+        <v>873310</v>
+      </c>
+      <c r="T14">
+        <v>847526</v>
+      </c>
+      <c r="U14">
+        <v>484743</v>
+      </c>
+      <c r="V14">
+        <v>551466</v>
+      </c>
+      <c r="W14">
+        <v>581334</v>
+      </c>
+      <c r="X14">
+        <v>193548</v>
+      </c>
+      <c r="Y14">
+        <v>537097</v>
+      </c>
+      <c r="Z14">
+        <v>1546873</v>
+      </c>
+      <c r="AA14">
+        <v>729035</v>
+      </c>
+      <c r="AB14">
+        <v>229936</v>
+      </c>
+      <c r="AC14">
+        <v>511134</v>
+      </c>
+      <c r="AD14">
+        <v>1561179</v>
+      </c>
+      <c r="AE14">
+        <v>524955</v>
+      </c>
+      <c r="AF14">
+        <v>1065756</v>
+      </c>
+      <c r="AG14">
+        <v>475239</v>
+      </c>
+      <c r="AH14">
+        <v>268513</v>
+      </c>
+      <c r="AI14">
+        <v>413397</v>
+      </c>
+      <c r="AJ14">
+        <v>192619</v>
+      </c>
+      <c r="AK14">
+        <v>643140</v>
+      </c>
+      <c r="AL14">
+        <v>805248</v>
+      </c>
+      <c r="AM14">
+        <v>721591</v>
+      </c>
+      <c r="AN14">
+        <v>322580</v>
+      </c>
+      <c r="AO14">
+        <v>1434298</v>
+      </c>
+      <c r="AP14">
+        <v>534328</v>
+      </c>
+      <c r="AQ14">
+        <v>424016</v>
+      </c>
+      <c r="AR14">
+        <v>642862</v>
+      </c>
+      <c r="AS14">
+        <v>512449</v>
+      </c>
+      <c r="AT14">
+        <v>522207</v>
+      </c>
+      <c r="AU14">
+        <v>1586656</v>
+      </c>
+      <c r="AV14">
+        <v>352727</v>
+      </c>
+      <c r="AW14">
+        <v>718961</v>
+      </c>
+      <c r="AX14">
+        <v>1152835</v>
+      </c>
+      <c r="AY14">
+        <v>984381</v>
+      </c>
+      <c r="AZ14">
+        <v>1804384</v>
+      </c>
+      <c r="BA14">
+        <v>962856</v>
+      </c>
+      <c r="BB14">
+        <v>1306210</v>
+      </c>
+      <c r="BC14">
+        <v>378530</v>
+      </c>
+      <c r="BD14">
+        <v>1472934</v>
+      </c>
+      <c r="BE14">
+        <v>1876347</v>
+      </c>
+      <c r="BF14">
+        <v>538013</v>
+      </c>
+      <c r="BG14">
+        <v>1595299</v>
+      </c>
+      <c r="BH14">
+        <v>1138067</v>
+      </c>
+      <c r="BI14">
+        <v>2647663</v>
+      </c>
+      <c r="BJ14">
+        <v>1397343</v>
+      </c>
+      <c r="BK14">
+        <v>1771499</v>
+      </c>
+      <c r="BL14">
+        <v>740600</v>
+      </c>
+      <c r="BM14">
+        <v>405515</v>
+      </c>
+      <c r="BN14">
+        <v>283352</v>
+      </c>
+      <c r="BO14">
+        <v>1295217</v>
+      </c>
+      <c r="BP14">
+        <v>478608</v>
+      </c>
+      <c r="BQ14">
+        <v>473786</v>
+      </c>
+      <c r="BR14">
+        <v>443408</v>
+      </c>
+      <c r="BS14">
+        <v>993496</v>
+      </c>
+      <c r="BT14">
+        <v>866068</v>
+      </c>
+      <c r="BU14">
+        <v>596165</v>
+      </c>
+      <c r="BV14">
+        <v>660147</v>
+      </c>
+      <c r="BW14">
+        <v>454252</v>
+      </c>
+      <c r="BX14">
+        <v>726836</v>
+      </c>
+      <c r="BY14">
+        <v>1061926</v>
+      </c>
+      <c r="BZ14">
+        <v>537843</v>
+      </c>
+      <c r="CA14">
+        <v>329026</v>
+      </c>
+    </row>
+    <row r="15" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>2020</v>
+      </c>
+      <c r="B15">
+        <v>66372831</v>
+      </c>
+      <c r="C15">
+        <v>5627243</v>
+      </c>
+      <c r="D15">
+        <v>1271065</v>
+      </c>
+      <c r="E15">
+        <v>819638</v>
+      </c>
+      <c r="F15">
+        <v>1170008</v>
+      </c>
+      <c r="G15">
+        <v>644869</v>
+      </c>
+      <c r="H15">
+        <v>278119</v>
+      </c>
+      <c r="I15">
+        <v>324544</v>
+      </c>
+      <c r="J15">
+        <v>749242</v>
+      </c>
+      <c r="K15">
+        <v>207172</v>
+      </c>
+      <c r="L15">
+        <v>720416</v>
+      </c>
+      <c r="M15">
+        <v>260416</v>
+      </c>
+      <c r="N15">
+        <v>494175</v>
+      </c>
+      <c r="O15">
+        <v>563614</v>
+      </c>
+      <c r="P15">
+        <v>1348177</v>
+      </c>
+      <c r="Q15">
+        <v>893751</v>
+      </c>
+      <c r="R15">
+        <v>920380</v>
+      </c>
+      <c r="S15">
+        <v>871207</v>
+      </c>
+      <c r="T15">
+        <v>842481</v>
+      </c>
+      <c r="U15">
+        <v>483692</v>
+      </c>
+      <c r="V15">
+        <v>552398</v>
+      </c>
+      <c r="W15">
+        <v>585451</v>
+      </c>
+      <c r="X15">
+        <v>192678</v>
+      </c>
+      <c r="Y15">
+        <v>536629</v>
+      </c>
+      <c r="Z15">
+        <v>1562593</v>
+      </c>
+      <c r="AA15">
+        <v>738139</v>
+      </c>
+      <c r="AB15">
+        <v>229247</v>
+      </c>
+      <c r="AC15">
+        <v>510256</v>
+      </c>
+      <c r="AD15">
+        <v>1556325</v>
+      </c>
+      <c r="AE15">
+        <v>523971</v>
+      </c>
+      <c r="AF15">
+        <v>1067867</v>
+      </c>
+      <c r="AG15">
+        <v>477254</v>
+      </c>
+      <c r="AH15">
+        <v>268509</v>
+      </c>
+      <c r="AI15">
+        <v>415527</v>
+      </c>
+      <c r="AJ15">
+        <v>193871</v>
+      </c>
+      <c r="AK15">
+        <v>641868</v>
+      </c>
+      <c r="AL15">
+        <v>806224</v>
+      </c>
+      <c r="AM15">
+        <v>725559</v>
+      </c>
+      <c r="AN15">
+        <v>323841</v>
+      </c>
+      <c r="AO15">
+        <v>1432288</v>
+      </c>
+      <c r="AP15">
+        <v>537466</v>
+      </c>
+      <c r="AQ15">
+        <v>423067</v>
+      </c>
+      <c r="AR15">
+        <v>640843</v>
+      </c>
+      <c r="AS15">
+        <v>511125</v>
+      </c>
+      <c r="AT15">
+        <v>519873</v>
+      </c>
+      <c r="AU15">
+        <v>1577315</v>
+      </c>
+      <c r="AV15">
+        <v>352043</v>
+      </c>
+      <c r="AW15">
+        <v>718169</v>
+      </c>
+      <c r="AX15">
+        <v>1150164</v>
+      </c>
+      <c r="AY15">
+        <v>980297</v>
+      </c>
+      <c r="AZ15">
+        <v>1798702</v>
+      </c>
+      <c r="BA15">
+        <v>958163</v>
+      </c>
+      <c r="BB15">
+        <v>1301926</v>
+      </c>
+      <c r="BC15">
+        <v>377317</v>
+      </c>
+      <c r="BD15">
+        <v>1465719</v>
+      </c>
+      <c r="BE15">
+        <v>1872422</v>
+      </c>
+      <c r="BF15">
+        <v>535900</v>
+      </c>
+      <c r="BG15">
+        <v>1588466</v>
+      </c>
+      <c r="BH15">
+        <v>1131140</v>
+      </c>
+      <c r="BI15">
+        <v>2641067</v>
+      </c>
+      <c r="BJ15">
+        <v>1387526</v>
+      </c>
+      <c r="BK15">
+        <v>1781812</v>
+      </c>
+      <c r="BL15">
+        <v>733640</v>
+      </c>
+      <c r="BM15">
+        <v>403542</v>
+      </c>
+      <c r="BN15">
+        <v>284343</v>
+      </c>
+      <c r="BO15">
+        <v>1296664</v>
+      </c>
+      <c r="BP15">
+        <v>477476</v>
+      </c>
+      <c r="BQ15">
+        <v>469856</v>
+      </c>
+      <c r="BR15">
+        <v>439537</v>
+      </c>
+      <c r="BS15">
+        <v>987196</v>
+      </c>
+      <c r="BT15">
+        <v>857364</v>
+      </c>
+      <c r="BU15">
+        <v>591477</v>
+      </c>
+      <c r="BV15">
+        <v>667942</v>
+      </c>
+      <c r="BW15">
+        <v>450923</v>
+      </c>
+      <c r="BX15">
+        <v>719993</v>
+      </c>
+      <c r="BY15">
+        <v>1050098</v>
+      </c>
+      <c r="BZ15">
+        <v>534311</v>
+      </c>
+      <c r="CA15">
+        <v>327243</v>
+      </c>
+    </row>
+    <row r="16" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>2021</v>
+      </c>
+      <c r="B16">
+        <v>66179083</v>
+      </c>
+      <c r="C16">
+        <v>5558108</v>
+      </c>
+      <c r="D16">
+        <v>1282690</v>
+      </c>
+      <c r="E16">
+        <v>819799</v>
+      </c>
+      <c r="F16">
+        <v>1183235</v>
+      </c>
+      <c r="G16">
+        <v>643895</v>
+      </c>
+      <c r="H16">
+        <v>275673</v>
+      </c>
+      <c r="I16">
+        <v>321454</v>
+      </c>
+      <c r="J16">
+        <v>741200</v>
+      </c>
+      <c r="K16">
+        <v>205211</v>
+      </c>
+      <c r="L16">
+        <v>722448</v>
+      </c>
+      <c r="M16">
+        <v>260256</v>
+      </c>
+      <c r="N16">
+        <v>494498</v>
+      </c>
+      <c r="O16">
+        <v>561459</v>
+      </c>
+      <c r="P16">
+        <v>1353964</v>
+      </c>
+      <c r="Q16">
+        <v>893014</v>
+      </c>
+      <c r="R16">
+        <v>921450</v>
+      </c>
+      <c r="S16">
+        <v>868797</v>
+      </c>
+      <c r="T16">
+        <v>836993</v>
+      </c>
+      <c r="U16">
+        <v>482534</v>
+      </c>
+      <c r="V16">
+        <v>551924</v>
+      </c>
+      <c r="W16">
+        <v>586494</v>
+      </c>
+      <c r="X16">
+        <v>191447</v>
+      </c>
+      <c r="Y16">
+        <v>536058</v>
+      </c>
+      <c r="Z16">
+        <v>1575278</v>
+      </c>
+      <c r="AA16">
+        <v>746433</v>
+      </c>
+      <c r="AB16">
+        <v>228456</v>
+      </c>
+      <c r="AC16">
+        <v>509344</v>
+      </c>
+      <c r="AD16">
+        <v>1550033</v>
+      </c>
+      <c r="AE16">
+        <v>522810</v>
+      </c>
+      <c r="AF16">
+        <v>1070096</v>
+      </c>
+      <c r="AG16">
+        <v>478561</v>
+      </c>
+      <c r="AH16">
+        <v>268123</v>
+      </c>
+      <c r="AI16">
+        <v>416629</v>
+      </c>
+      <c r="AJ16">
+        <v>194473</v>
+      </c>
+      <c r="AK16">
+        <v>640182</v>
+      </c>
+      <c r="AL16">
+        <v>807045</v>
+      </c>
+      <c r="AM16">
+        <v>727799</v>
+      </c>
+      <c r="AN16">
+        <v>324467</v>
+      </c>
+      <c r="AO16">
+        <v>1430073</v>
+      </c>
+      <c r="AP16">
+        <v>540458</v>
+      </c>
+      <c r="AQ16">
+        <v>422019</v>
+      </c>
+      <c r="AR16">
+        <v>638734</v>
+      </c>
+      <c r="AS16">
+        <v>509236</v>
+      </c>
+      <c r="AT16">
+        <v>517140</v>
+      </c>
+      <c r="AU16">
+        <v>1567247</v>
+      </c>
+      <c r="AV16">
+        <v>351198</v>
+      </c>
+      <c r="AW16">
+        <v>717121</v>
+      </c>
+      <c r="AX16">
+        <v>1146612</v>
+      </c>
+      <c r="AY16">
+        <v>976373</v>
+      </c>
+      <c r="AZ16">
+        <v>1792697</v>
+      </c>
+      <c r="BA16">
+        <v>950985</v>
+      </c>
+      <c r="BB16">
+        <v>1297326</v>
+      </c>
+      <c r="BC16">
+        <v>376273</v>
+      </c>
+      <c r="BD16">
+        <v>1458068</v>
+      </c>
+      <c r="BE16">
+        <v>1867608</v>
+      </c>
+      <c r="BF16">
+        <v>533948</v>
+      </c>
+      <c r="BG16">
+        <v>1580495</v>
+      </c>
+      <c r="BH16">
+        <v>1123595</v>
+      </c>
+      <c r="BI16">
+        <v>2633681</v>
+      </c>
+      <c r="BJ16">
+        <v>1377226</v>
+      </c>
+      <c r="BK16">
+        <v>1786877</v>
+      </c>
+      <c r="BL16">
+        <v>726821</v>
+      </c>
+      <c r="BM16">
+        <v>401574</v>
+      </c>
+      <c r="BN16">
+        <v>285232</v>
+      </c>
+      <c r="BO16">
+        <v>1296725</v>
+      </c>
+      <c r="BP16">
+        <v>476300</v>
+      </c>
+      <c r="BQ16">
+        <v>465930</v>
+      </c>
+      <c r="BR16">
+        <v>435965</v>
+      </c>
+      <c r="BS16">
+        <v>980156</v>
+      </c>
+      <c r="BT16">
+        <v>848432</v>
+      </c>
+      <c r="BU16">
+        <v>586617</v>
+      </c>
+      <c r="BV16">
+        <v>673423</v>
+      </c>
+      <c r="BW16">
+        <v>447446</v>
+      </c>
+      <c r="BX16">
+        <v>713130</v>
+      </c>
+      <c r="BY16">
+        <v>1037668</v>
+      </c>
+      <c r="BZ16">
+        <v>530852</v>
+      </c>
+      <c r="CA16">
+        <v>325492</v>
+      </c>
+    </row>
+    <row r="17" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>2022</v>
+      </c>
+      <c r="B17">
+        <v>66171439</v>
+      </c>
+      <c r="C17">
+        <v>5527994</v>
+      </c>
+      <c r="D17">
+        <v>1288637</v>
+      </c>
+      <c r="E17">
+        <v>820512</v>
+      </c>
+      <c r="F17">
+        <v>1190060</v>
+      </c>
+      <c r="G17">
+        <v>643963</v>
+      </c>
+      <c r="H17">
+        <v>274763</v>
+      </c>
+      <c r="I17">
+        <v>320432</v>
+      </c>
+      <c r="J17">
+        <v>739473</v>
+      </c>
+      <c r="K17">
+        <v>204526</v>
+      </c>
+      <c r="L17">
+        <v>724178</v>
+      </c>
+      <c r="M17">
+        <v>260433</v>
+      </c>
+      <c r="N17">
+        <v>495325</v>
+      </c>
+      <c r="O17">
+        <v>561992</v>
+      </c>
+      <c r="P17">
+        <v>1356449</v>
+      </c>
+      <c r="Q17">
+        <v>894054</v>
+      </c>
+      <c r="R17">
+        <v>922171</v>
+      </c>
+      <c r="S17">
+        <v>868281</v>
+      </c>
+      <c r="T17">
+        <v>835360</v>
+      </c>
+      <c r="U17">
+        <v>482875</v>
+      </c>
+      <c r="V17">
+        <v>553171</v>
+      </c>
+      <c r="W17">
+        <v>586789</v>
+      </c>
+      <c r="X17">
+        <v>190842</v>
+      </c>
+      <c r="Y17">
+        <v>536557</v>
+      </c>
+      <c r="Z17">
+        <v>1583672</v>
+      </c>
+      <c r="AA17">
+        <v>751343</v>
+      </c>
+      <c r="AB17">
+        <v>228376</v>
+      </c>
+      <c r="AC17">
+        <v>509479</v>
+      </c>
+      <c r="AD17">
+        <v>1549344</v>
+      </c>
+      <c r="AE17">
+        <v>522541</v>
+      </c>
+      <c r="AF17">
+        <v>1072464</v>
+      </c>
+      <c r="AG17">
+        <v>479351</v>
+      </c>
+      <c r="AH17">
+        <v>268016</v>
+      </c>
+      <c r="AI17">
+        <v>418785</v>
+      </c>
+      <c r="AJ17">
+        <v>194573</v>
+      </c>
+      <c r="AK17">
+        <v>639788</v>
+      </c>
+      <c r="AL17">
+        <v>809660</v>
+      </c>
+      <c r="AM17">
+        <v>729581</v>
+      </c>
+      <c r="AN17">
+        <v>324835</v>
+      </c>
+      <c r="AO17">
+        <v>1431536</v>
+      </c>
+      <c r="AP17">
+        <v>542314</v>
+      </c>
+      <c r="AQ17">
+        <v>421995</v>
+      </c>
+      <c r="AR17">
+        <v>638732</v>
+      </c>
+      <c r="AS17">
+        <v>509001</v>
+      </c>
+      <c r="AT17">
+        <v>516843</v>
+      </c>
+      <c r="AU17">
+        <v>1566510</v>
+      </c>
+      <c r="AV17">
+        <v>351484</v>
+      </c>
+      <c r="AW17">
+        <v>717040</v>
+      </c>
+      <c r="AX17">
+        <v>1146286</v>
+      </c>
+      <c r="AY17">
+        <v>975570</v>
+      </c>
+      <c r="AZ17">
+        <v>1790863</v>
+      </c>
+      <c r="BA17">
+        <v>948310</v>
+      </c>
+      <c r="BB17">
+        <v>1296013</v>
+      </c>
+      <c r="BC17">
+        <v>376350</v>
+      </c>
+      <c r="BD17">
+        <v>1457556</v>
+      </c>
+      <c r="BE17">
+        <v>1868519</v>
+      </c>
+      <c r="BF17">
+        <v>533394</v>
+      </c>
+      <c r="BG17">
+        <v>1579805</v>
+      </c>
+      <c r="BH17">
+        <v>1122265</v>
+      </c>
+      <c r="BI17">
+        <v>2634154</v>
+      </c>
+      <c r="BJ17">
+        <v>1376230</v>
+      </c>
+      <c r="BK17">
+        <v>1789385</v>
+      </c>
+      <c r="BL17">
+        <v>724678</v>
+      </c>
+      <c r="BM17">
+        <v>401139</v>
+      </c>
+      <c r="BN17">
+        <v>285916</v>
+      </c>
+      <c r="BO17">
+        <v>1298425</v>
+      </c>
+      <c r="BP17">
+        <v>475875</v>
+      </c>
+      <c r="BQ17">
+        <v>464505</v>
+      </c>
+      <c r="BR17">
+        <v>434580</v>
+      </c>
+      <c r="BS17">
+        <v>978372</v>
+      </c>
+      <c r="BT17">
+        <v>847384</v>
+      </c>
+      <c r="BU17">
+        <v>585352</v>
+      </c>
+      <c r="BV17">
+        <v>676583</v>
+      </c>
+      <c r="BW17">
+        <v>446148</v>
+      </c>
+      <c r="BX17">
+        <v>712143</v>
+      </c>
+      <c r="BY17">
+        <v>1035028</v>
+      </c>
+      <c r="BZ17">
+        <v>529395</v>
+      </c>
+      <c r="CA17">
+        <v>325116</v>
+      </c>
+    </row>
+    <row r="18" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>2023</v>
+      </c>
+      <c r="B18">
+        <v>66130957</v>
+      </c>
+      <c r="C18">
+        <v>5511463</v>
+      </c>
+      <c r="D18">
+        <v>1292276</v>
+      </c>
+      <c r="E18">
+        <v>820464</v>
+      </c>
+      <c r="F18">
+        <v>1195796</v>
+      </c>
+      <c r="G18">
+        <v>641272</v>
+      </c>
+      <c r="H18">
+        <v>273675</v>
+      </c>
+      <c r="I18">
+        <v>319370</v>
+      </c>
+      <c r="J18">
+        <v>737382</v>
+      </c>
+      <c r="K18">
+        <v>203661</v>
+      </c>
+      <c r="L18">
+        <v>725433</v>
+      </c>
+      <c r="M18">
+        <v>260419</v>
+      </c>
+      <c r="N18">
+        <v>496551</v>
+      </c>
+      <c r="O18">
+        <v>562404</v>
+      </c>
+      <c r="P18">
+        <v>1358338</v>
+      </c>
+      <c r="Q18">
+        <v>894168</v>
+      </c>
+      <c r="R18">
+        <v>922026</v>
+      </c>
+      <c r="S18">
+        <v>867043</v>
+      </c>
+      <c r="T18">
+        <v>833027</v>
+      </c>
+      <c r="U18">
+        <v>482912</v>
+      </c>
+      <c r="V18">
+        <v>553234</v>
+      </c>
+      <c r="W18">
+        <v>588108</v>
+      </c>
+      <c r="X18">
+        <v>190147</v>
+      </c>
+      <c r="Y18">
+        <v>536351</v>
+      </c>
+      <c r="Z18">
+        <v>1589214</v>
+      </c>
+      <c r="AA18">
+        <v>755364</v>
+      </c>
+      <c r="AB18">
+        <v>228092</v>
+      </c>
+      <c r="AC18">
+        <v>509433</v>
+      </c>
+      <c r="AD18">
+        <v>1547246</v>
+      </c>
+      <c r="AE18">
+        <v>522080</v>
+      </c>
+      <c r="AF18">
+        <v>1073064</v>
+      </c>
+      <c r="AG18">
+        <v>479705</v>
+      </c>
+      <c r="AH18">
+        <v>267729</v>
+      </c>
+      <c r="AI18">
+        <v>418339</v>
+      </c>
+      <c r="AJ18">
+        <v>194400</v>
+      </c>
+      <c r="AK18">
+        <v>638997</v>
+      </c>
+      <c r="AL18">
+        <v>811891</v>
+      </c>
+      <c r="AM18">
+        <v>731269</v>
+      </c>
+      <c r="AN18">
+        <v>325069</v>
+      </c>
+      <c r="AO18">
+        <v>1431300</v>
+      </c>
+      <c r="AP18">
+        <v>544114</v>
+      </c>
+      <c r="AQ18">
+        <v>421840</v>
+      </c>
+      <c r="AR18">
+        <v>638037</v>
+      </c>
+      <c r="AS18">
+        <v>508664</v>
+      </c>
+      <c r="AT18">
+        <v>516320</v>
+      </c>
+      <c r="AU18">
+        <v>1564780</v>
+      </c>
+      <c r="AV18">
+        <v>351537</v>
+      </c>
+      <c r="AW18">
+        <v>716844</v>
+      </c>
+      <c r="AX18">
+        <v>1145737</v>
+      </c>
+      <c r="AY18">
+        <v>973835</v>
+      </c>
+      <c r="AZ18">
+        <v>1787752</v>
+      </c>
+      <c r="BA18">
+        <v>946457</v>
+      </c>
+      <c r="BB18">
+        <v>1293572</v>
+      </c>
+      <c r="BC18">
+        <v>375866</v>
+      </c>
+      <c r="BD18">
+        <v>1456144</v>
+      </c>
+      <c r="BE18">
+        <v>1869163</v>
+      </c>
+      <c r="BF18">
+        <v>532497</v>
+      </c>
+      <c r="BG18">
+        <v>1578361</v>
+      </c>
+      <c r="BH18">
+        <v>1120095</v>
+      </c>
+      <c r="BI18">
+        <v>2632106</v>
+      </c>
+      <c r="BJ18">
+        <v>1374571</v>
+      </c>
+      <c r="BK18">
+        <v>1790929</v>
+      </c>
+      <c r="BL18">
+        <v>721734</v>
+      </c>
+      <c r="BM18">
+        <v>400348</v>
+      </c>
+      <c r="BN18">
+        <v>286350</v>
+      </c>
+      <c r="BO18">
+        <v>1299030</v>
+      </c>
+      <c r="BP18">
+        <v>475207</v>
+      </c>
+      <c r="BQ18">
+        <v>462968</v>
+      </c>
+      <c r="BR18">
+        <v>432624</v>
+      </c>
+      <c r="BS18">
+        <v>975879</v>
+      </c>
+      <c r="BT18">
+        <v>845938</v>
+      </c>
+      <c r="BU18">
+        <v>583502</v>
+      </c>
+      <c r="BV18">
+        <v>680361</v>
+      </c>
+      <c r="BW18">
+        <v>444548</v>
+      </c>
+      <c r="BX18">
+        <v>710458</v>
+      </c>
+      <c r="BY18">
+        <v>1031921</v>
+      </c>
+      <c r="BZ18">
+        <v>527669</v>
+      </c>
+      <c r="CA18">
+        <v>324487</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B43F17DC-DBF5-4168-94ED-472017971344}">
   <dimension ref="A1:X33"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.125" customWidth="1"/>
-    <col min="2" max="2" width="12.625" customWidth="1"/>
-    <col min="3" max="12" width="10.375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.5" customWidth="1"/>
-    <col min="14" max="14" width="13.75" customWidth="1"/>
-    <col min="15" max="15" width="10.375" customWidth="1"/>
-    <col min="16" max="16" width="13.875" customWidth="1"/>
-    <col min="23" max="23" width="10.875" customWidth="1"/>
-    <col min="24" max="24" width="11.375" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" customWidth="1"/>
+    <col min="3" max="12" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.44140625" customWidth="1"/>
+    <col min="14" max="14" width="13.77734375" customWidth="1"/>
+    <col min="15" max="15" width="10.33203125" customWidth="1"/>
+    <col min="16" max="16" width="13.88671875" customWidth="1"/>
+    <col min="23" max="23" width="10.88671875" customWidth="1"/>
+    <col min="24" max="24" width="11.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="27.75" x14ac:dyDescent="0.4">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:24" ht="28.2" x14ac:dyDescent="0.5">
+      <c r="A1" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="8"/>
-      <c r="N1" s="8"/>
-      <c r="O1" s="8"/>
-      <c r="P1" s="8"/>
-      <c r="Q1" s="8"/>
-      <c r="R1" s="8"/>
-      <c r="S1" s="8"/>
-      <c r="T1" s="8"/>
-      <c r="U1" s="8"/>
-      <c r="V1" s="8"/>
-      <c r="W1" s="8"/>
-      <c r="X1" s="8"/>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
+      <c r="S1" s="10"/>
+      <c r="T1" s="10"/>
+      <c r="U1" s="10"/>
+      <c r="V1" s="10"/>
+      <c r="W1" s="10"/>
+      <c r="X1" s="10"/>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -2547,7 +7082,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2022</v>
       </c>
@@ -2591,7 +7126,7 @@
         <v>4866495</v>
       </c>
       <c r="O3" s="3">
-        <f t="shared" ref="O3:O7" si="0">SUM(P3:W3)</f>
+        <f t="shared" ref="O3:O4" si="0">SUM(P3:W3)</f>
         <v>10906788</v>
       </c>
       <c r="P3" s="7">
@@ -2623,7 +7158,7 @@
         <v>82605828</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2023</v>
       </c>
@@ -2699,47 +7234,47 @@
         <v>83261378</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B5" s="1"/>
       <c r="O5" s="2"/>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B6" s="1"/>
       <c r="O6" s="2"/>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B7" s="1"/>
       <c r="O7" s="2"/>
     </row>
-    <row r="8" spans="1:24" ht="27.75" x14ac:dyDescent="0.4">
-      <c r="A8" s="8" t="s">
+    <row r="8" spans="1:24" ht="28.2" x14ac:dyDescent="0.5">
+      <c r="A8" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="8"/>
-      <c r="Q8" s="8"/>
-      <c r="R8" s="8"/>
-      <c r="S8" s="8"/>
-      <c r="T8" s="8"/>
-      <c r="U8" s="8"/>
-      <c r="V8" s="8"/>
-      <c r="W8" s="8"/>
-      <c r="X8" s="8"/>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="10"/>
+      <c r="P8" s="10"/>
+      <c r="Q8" s="10"/>
+      <c r="R8" s="10"/>
+      <c r="S8" s="10"/>
+      <c r="T8" s="10"/>
+      <c r="U8" s="10"/>
+      <c r="V8" s="10"/>
+      <c r="W8" s="10"/>
+      <c r="X8" s="10"/>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -2813,7 +7348,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2022</v>
       </c>
@@ -2910,7 +7445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2023</v>
       </c>
@@ -3007,44 +7542,44 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B12" s="1"/>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B13" s="1"/>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B14" s="1"/>
     </row>
-    <row r="15" spans="1:24" ht="27.75" x14ac:dyDescent="0.4">
-      <c r="A15" s="8" t="s">
+    <row r="15" spans="1:24" ht="28.2" x14ac:dyDescent="0.5">
+      <c r="A15" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="8"/>
-      <c r="N15" s="8"/>
-      <c r="O15" s="8"/>
-      <c r="P15" s="8"/>
-      <c r="Q15" s="8"/>
-      <c r="R15" s="8"/>
-      <c r="S15" s="8"/>
-      <c r="T15" s="8"/>
-      <c r="U15" s="8"/>
-      <c r="V15" s="8"/>
-      <c r="W15" s="8"/>
-      <c r="X15" s="8"/>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="10"/>
+      <c r="O15" s="10"/>
+      <c r="P15" s="10"/>
+      <c r="Q15" s="10"/>
+      <c r="R15" s="10"/>
+      <c r="S15" s="10"/>
+      <c r="T15" s="10"/>
+      <c r="U15" s="10"/>
+      <c r="V15" s="10"/>
+      <c r="W15" s="10"/>
+      <c r="X15" s="10"/>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -3102,7 +7637,7 @@
       <c r="W16" s="7"/>
       <c r="X16" s="7"/>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2022</v>
       </c>
@@ -3174,7 +7709,7 @@
       <c r="W17" s="2"/>
       <c r="X17" s="2"/>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2023</v>
       </c>
@@ -3246,49 +7781,49 @@
       <c r="W18" s="2"/>
       <c r="X18" s="2"/>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B19" s="1"/>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B20" s="1"/>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B21" s="1"/>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B22" s="1"/>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B23" s="1"/>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B24" s="1"/>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B25" s="1"/>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B26" s="1"/>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B27" s="1"/>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B28" s="1"/>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B29" s="1"/>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B30" s="1"/>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B31" s="1"/>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B32" s="1"/>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B33" s="1"/>
     </row>
   </sheetData>
@@ -3305,14 +7840,4 @@
     <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41BEA482-6B4D-415D-9895-A94933E586DE}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>